--- a/packages/GB Accounts Self Employed 2023-04-05 (Apr23) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Self Employed 2023-04-05 (Apr23) Excel 2007/Fixedassets.xlsx
@@ -1357,6 +1357,11 @@
             <v>0.18</v>
           </cell>
         </row>
+        <row r="6">
+          <cell r="G6">
+            <v>0.06</v>
+          </cell>
+        </row>
         <row r="8"/>
         <row r="13">
           <cell r="G13">
@@ -1776,7 +1781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA111"/>
+  <dimension ref="A1:AC111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="5" customWidth="1"/>
@@ -1805,9 +1810,11 @@
     <col min="25" max="26" width="9.1640625" style="2"/>
     <col min="27" max="27" width="1.6640625" style="5" customWidth="1"/>
     <col min="28" max="16384" width="9.1640625" style="5"/>
+    <col min="28" max="28" width="5.6640625" style="89" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="123"/>
       <c r="B1" s="134" t="s">
         <v>0</v>
@@ -1892,8 +1899,13 @@
         <v>0</v>
       </c>
       <c r="AA1" s="21"/>
-    </row>
-    <row r="2" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="20">
+        <f>AC57+AC110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="124"/>
       <c r="B2" s="134"/>
       <c r="C2" s="135" t="s">
@@ -1955,8 +1967,18 @@
         <v>51</v>
       </c>
       <c r="AA2" s="22"/>
-    </row>
-    <row r="3" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB2" s="130" t="inlineStr">
+        <is>
+          <t>Pool (S = special rate)</t>
+        </is>
+      </c>
+      <c r="AC2" s="132" t="inlineStr">
+        <is>
+          <t>Special Rate W Down Allowance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="124"/>
       <c r="B3" s="134"/>
       <c r="C3" s="136"/>
@@ -1985,7 +2007,7 @@
       <c r="Z3" s="132"/>
       <c r="AA3" s="22"/>
     </row>
-    <row r="4" spans="1:27" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:29" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="124"/>
       <c r="B4" s="134"/>
       <c r="C4" s="136"/>
@@ -2037,8 +2059,13 @@
       <c r="Y4" s="132"/>
       <c r="Z4" s="132"/>
       <c r="AA4" s="23"/>
-    </row>
-    <row r="5" spans="1:27" s="16" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AB4" s="23"/>
+      <c r="AC4" s="15">
+        <f>[1]Admin!$G$6</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" s="16" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="100"/>
       <c r="B5" s="55"/>
       <c r="C5" s="74"/>
@@ -2067,7 +2094,7 @@
       <c r="Z5" s="57"/>
       <c r="AA5" s="23"/>
     </row>
-    <row r="6" spans="1:27" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="101"/>
       <c r="B6" s="152" t="s">
         <v>61</v>
@@ -2101,7 +2128,7 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="101"/>
       <c r="B7" s="122" t="s">
         <v>10</v>
@@ -2135,7 +2162,7 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="22"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A8" s="101"/>
       <c r="B8" s="42"/>
       <c r="C8" s="75"/>
@@ -2185,7 +2212,7 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="22"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A9" s="101"/>
       <c r="B9" s="42"/>
       <c r="C9" s="75"/>
@@ -2235,7 +2262,7 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="22"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A10" s="101"/>
       <c r="B10" s="42"/>
       <c r="C10" s="75"/>
@@ -2285,7 +2312,7 @@
       <c r="Z10" s="11"/>
       <c r="AA10" s="22"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A11" s="101"/>
       <c r="B11" s="117" t="s">
         <v>67</v>
@@ -2360,8 +2387,13 @@
         <v>0</v>
       </c>
       <c r="AA11" s="22"/>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="17">
+        <f>SUM(AC8:AC10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="101"/>
       <c r="B12" s="37"/>
       <c r="C12" s="76"/>
@@ -2390,7 +2422,7 @@
       <c r="Z12" s="7"/>
       <c r="AA12" s="22"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A13" s="101"/>
       <c r="B13" s="122" t="s">
         <v>9</v>
@@ -2424,7 +2456,7 @@
       <c r="Z13" s="11"/>
       <c r="AA13" s="22"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A14" s="101"/>
       <c r="B14" s="42"/>
       <c r="C14" s="75"/>
@@ -2458,11 +2490,11 @@
       <c r="P14" s="88"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="11" t="str">
-        <f>IF(O14&gt;0,O14*R$4," ")</f>
+        <f>IF(AND(O14&gt;0,AB14&lt;&gt;"S"),O14*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S14" s="11" t="str">
-        <f>IF(O14&gt;0,O14-R14," ")</f>
+        <f>IF(O14&gt;0,O14-N(R14)-N(AC14)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T14" s="11"/>
@@ -2485,8 +2517,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA14" s="22"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB14" s="42"/>
+      <c r="AC14" s="11" t="str">
+        <f>IF(AND(O14&gt;0,AB14="S"),O14*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A15" s="101"/>
       <c r="B15" s="42"/>
       <c r="C15" s="75"/>
@@ -2520,11 +2557,11 @@
       <c r="P15" s="88"/>
       <c r="Q15" s="11"/>
       <c r="R15" s="11" t="str">
-        <f>IF(O15&gt;0,O15*R$4," ")</f>
+        <f>IF(AND(O15&gt;0,AB15&lt;&gt;"S"),O15*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S15" s="11" t="str">
-        <f>IF(O15&gt;0,O15-R15," ")</f>
+        <f>IF(O15&gt;0,O15-N(R15)-N(AC15)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T15" s="11"/>
@@ -2547,8 +2584,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA15" s="22"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB15" s="42"/>
+      <c r="AC15" s="11" t="str">
+        <f>IF(AND(O15&gt;0,AB15="S"),O15*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A16" s="101"/>
       <c r="B16" s="42"/>
       <c r="C16" s="75"/>
@@ -2582,11 +2624,11 @@
       <c r="P16" s="88"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="11" t="str">
-        <f>IF(O16&gt;0,O16*R$4," ")</f>
+        <f>IF(AND(O16&gt;0,AB16&lt;&gt;"S"),O16*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S16" s="11" t="str">
-        <f>IF(O16&gt;0,O16-R16," ")</f>
+        <f>IF(O16&gt;0,O16-N(R16)-N(AC16)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T16" s="11"/>
@@ -2609,8 +2651,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA16" s="22"/>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB16" s="42"/>
+      <c r="AC16" s="11" t="str">
+        <f>IF(AND(O16&gt;0,AB16="S"),O16*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A17" s="101"/>
       <c r="B17" s="42"/>
       <c r="C17" s="75"/>
@@ -2644,11 +2691,11 @@
       <c r="P17" s="88"/>
       <c r="Q17" s="11"/>
       <c r="R17" s="11" t="str">
-        <f>IF(O17&gt;0,O17*R$4," ")</f>
+        <f>IF(AND(O17&gt;0,AB17&lt;&gt;"S"),O17*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S17" s="11" t="str">
-        <f>IF(O17&gt;0,O17-R17," ")</f>
+        <f>IF(O17&gt;0,O17-N(R17)-N(AC17)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T17" s="11"/>
@@ -2671,8 +2718,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA17" s="22"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB17" s="42"/>
+      <c r="AC17" s="11" t="str">
+        <f>IF(AND(O17&gt;0,AB17="S"),O17*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A18" s="101"/>
       <c r="B18" s="42"/>
       <c r="C18" s="75"/>
@@ -2706,11 +2758,11 @@
       <c r="P18" s="88"/>
       <c r="Q18" s="11"/>
       <c r="R18" s="11" t="str">
-        <f>IF(O18&gt;0,O18*R$4," ")</f>
+        <f>IF(AND(O18&gt;0,AB18&lt;&gt;"S"),O18*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S18" s="11" t="str">
-        <f>IF(O18&gt;0,O18-R18," ")</f>
+        <f>IF(O18&gt;0,O18-N(R18)-N(AC18)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T18" s="11"/>
@@ -2733,8 +2785,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA18" s="22"/>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB18" s="42"/>
+      <c r="AC18" s="11" t="str">
+        <f>IF(AND(O18&gt;0,AB18="S"),O18*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A19" s="101"/>
       <c r="B19" s="117" t="s">
         <v>68</v>
@@ -2809,8 +2866,13 @@
         <v>0</v>
       </c>
       <c r="AA19" s="22"/>
-    </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="17">
+        <f>SUM(AC14:AC18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="101"/>
       <c r="B20" s="37"/>
       <c r="C20" s="76"/>
@@ -2839,7 +2901,7 @@
       <c r="Z20" s="7"/>
       <c r="AA20" s="22"/>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A21" s="101"/>
       <c r="B21" s="122" t="s">
         <v>55</v>
@@ -2873,7 +2935,7 @@
       <c r="Z21" s="11"/>
       <c r="AA21" s="22"/>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A22" s="101"/>
       <c r="B22" s="42"/>
       <c r="C22" s="75"/>
@@ -2907,11 +2969,11 @@
       <c r="P22" s="88"/>
       <c r="Q22" s="11"/>
       <c r="R22" s="11" t="str">
-        <f>IF(O22&gt;0,O22*R$4," ")</f>
+        <f>IF(AND(O22&gt;0,AB22&lt;&gt;"S"),O22*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S22" s="11" t="str">
-        <f>IF(O22&gt;0,O22-R22," ")</f>
+        <f>IF(O22&gt;0,O22-N(R22)-N(AC22)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T22" s="11"/>
@@ -2934,8 +2996,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA22" s="22"/>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB22" s="42"/>
+      <c r="AC22" s="11" t="str">
+        <f>IF(AND(O22&gt;0,AB22="S"),O22*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A23" s="101"/>
       <c r="B23" s="42"/>
       <c r="C23" s="75"/>
@@ -2969,11 +3036,11 @@
       <c r="P23" s="88"/>
       <c r="Q23" s="11"/>
       <c r="R23" s="11" t="str">
-        <f>IF(O23&gt;0,O23*R$4," ")</f>
+        <f>IF(AND(O23&gt;0,AB23&lt;&gt;"S"),O23*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S23" s="11" t="str">
-        <f>IF(O23&gt;0,O23-R23," ")</f>
+        <f>IF(O23&gt;0,O23-N(R23)-N(AC23)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T23" s="11"/>
@@ -2996,8 +3063,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA23" s="22"/>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB23" s="42"/>
+      <c r="AC23" s="11" t="str">
+        <f>IF(AND(O23&gt;0,AB23="S"),O23*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A24" s="101"/>
       <c r="B24" s="42"/>
       <c r="C24" s="75"/>
@@ -3031,11 +3103,11 @@
       <c r="P24" s="88"/>
       <c r="Q24" s="11"/>
       <c r="R24" s="11" t="str">
-        <f>IF(O24&gt;0,O24*R$4," ")</f>
+        <f>IF(AND(O24&gt;0,AB24&lt;&gt;"S"),O24*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S24" s="11" t="str">
-        <f>IF(O24&gt;0,O24-R24," ")</f>
+        <f>IF(O24&gt;0,O24-N(R24)-N(AC24)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T24" s="11"/>
@@ -3058,8 +3130,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA24" s="22"/>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB24" s="42"/>
+      <c r="AC24" s="11" t="str">
+        <f>IF(AND(O24&gt;0,AB24="S"),O24*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A25" s="101"/>
       <c r="B25" s="42"/>
       <c r="C25" s="75"/>
@@ -3093,11 +3170,11 @@
       <c r="P25" s="88"/>
       <c r="Q25" s="11"/>
       <c r="R25" s="11" t="str">
-        <f>IF(O25&gt;0,O25*R$4," ")</f>
+        <f>IF(AND(O25&gt;0,AB25&lt;&gt;"S"),O25*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S25" s="11" t="str">
-        <f>IF(O25&gt;0,O25-R25," ")</f>
+        <f>IF(O25&gt;0,O25-N(R25)-N(AC25)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T25" s="11"/>
@@ -3120,8 +3197,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA25" s="22"/>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB25" s="42"/>
+      <c r="AC25" s="11" t="str">
+        <f>IF(AND(O25&gt;0,AB25="S"),O25*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A26" s="101"/>
       <c r="B26" s="42"/>
       <c r="C26" s="75"/>
@@ -3155,11 +3237,11 @@
       <c r="P26" s="88"/>
       <c r="Q26" s="11"/>
       <c r="R26" s="11" t="str">
-        <f>IF(O26&gt;0,O26*R$4," ")</f>
+        <f>IF(AND(O26&gt;0,AB26&lt;&gt;"S"),O26*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S26" s="11" t="str">
-        <f>IF(O26&gt;0,O26-R26," ")</f>
+        <f>IF(O26&gt;0,O26-N(R26)-N(AC26)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T26" s="11"/>
@@ -3182,8 +3264,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA26" s="22"/>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB26" s="42"/>
+      <c r="AC26" s="11" t="str">
+        <f>IF(AND(O26&gt;0,AB26="S"),O26*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A27" s="101"/>
       <c r="B27" s="117" t="s">
         <v>69</v>
@@ -3258,8 +3345,13 @@
         <v>0</v>
       </c>
       <c r="AA27" s="22"/>
-    </row>
-    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="17">
+        <f>SUM(AC22:AC26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="101"/>
       <c r="B28" s="37"/>
       <c r="C28" s="76"/>
@@ -3288,7 +3380,7 @@
       <c r="Z28" s="7"/>
       <c r="AA28" s="22"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A29" s="101"/>
       <c r="B29" s="122" t="s">
         <v>7</v>
@@ -3322,7 +3414,7 @@
       <c r="Z29" s="11"/>
       <c r="AA29" s="22"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A30" s="101"/>
       <c r="B30" s="42"/>
       <c r="C30" s="75"/>
@@ -3356,11 +3448,11 @@
       <c r="P30" s="88"/>
       <c r="Q30" s="11"/>
       <c r="R30" s="11" t="str">
-        <f>IF(O30&gt;0,O30*R$4," ")</f>
+        <f>IF(AND(O30&gt;0,AB30&lt;&gt;"S"),O30*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S30" s="11" t="str">
-        <f>IF(O30&gt;0,O30-R30," ")</f>
+        <f>IF(O30&gt;0,O30-N(R30)-N(AC30)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T30" s="11"/>
@@ -3383,8 +3475,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA30" s="22"/>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB30" s="42"/>
+      <c r="AC30" s="11" t="str">
+        <f>IF(AND(O30&gt;0,AB30="S"),O30*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A31" s="101"/>
       <c r="B31" s="42"/>
       <c r="C31" s="75"/>
@@ -3418,11 +3515,11 @@
       <c r="P31" s="88"/>
       <c r="Q31" s="11"/>
       <c r="R31" s="11" t="str">
-        <f>IF(O31&gt;0,O31*R$4," ")</f>
+        <f>IF(AND(O31&gt;0,AB31&lt;&gt;"S"),O31*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S31" s="11" t="str">
-        <f>IF(O31&gt;0,O31-R31," ")</f>
+        <f>IF(O31&gt;0,O31-N(R31)-N(AC31)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T31" s="11"/>
@@ -3445,8 +3542,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA31" s="22"/>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB31" s="42"/>
+      <c r="AC31" s="11" t="str">
+        <f>IF(AND(O31&gt;0,AB31="S"),O31*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A32" s="101"/>
       <c r="B32" s="42"/>
       <c r="C32" s="75"/>
@@ -3480,11 +3582,11 @@
       <c r="P32" s="88"/>
       <c r="Q32" s="11"/>
       <c r="R32" s="11" t="str">
-        <f>IF(O32&gt;0,O32*R$4," ")</f>
+        <f>IF(AND(O32&gt;0,AB32&lt;&gt;"S"),O32*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S32" s="11" t="str">
-        <f>IF(O32&gt;0,O32-R32," ")</f>
+        <f>IF(O32&gt;0,O32-N(R32)-N(AC32)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T32" s="11"/>
@@ -3507,8 +3609,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA32" s="22"/>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB32" s="42"/>
+      <c r="AC32" s="11" t="str">
+        <f>IF(AND(O32&gt;0,AB32="S"),O32*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A33" s="101"/>
       <c r="B33" s="42"/>
       <c r="C33" s="75"/>
@@ -3542,11 +3649,11 @@
       <c r="P33" s="88"/>
       <c r="Q33" s="11"/>
       <c r="R33" s="11" t="str">
-        <f>IF(O33&gt;0,O33*R$4," ")</f>
+        <f>IF(AND(O33&gt;0,AB33&lt;&gt;"S"),O33*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S33" s="11" t="str">
-        <f>IF(O33&gt;0,O33-R33," ")</f>
+        <f>IF(O33&gt;0,O33-N(R33)-N(AC33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T33" s="11"/>
@@ -3569,8 +3676,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA33" s="22"/>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB33" s="42"/>
+      <c r="AC33" s="11" t="str">
+        <f>IF(AND(O33&gt;0,AB33="S"),O33*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A34" s="101"/>
       <c r="B34" s="42"/>
       <c r="C34" s="75"/>
@@ -3604,11 +3716,11 @@
       <c r="P34" s="88"/>
       <c r="Q34" s="11"/>
       <c r="R34" s="11" t="str">
-        <f>IF(O34&gt;0,O34*R$4," ")</f>
+        <f>IF(AND(O34&gt;0,AB34&lt;&gt;"S"),O34*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S34" s="11" t="str">
-        <f>IF(O34&gt;0,O34-R34," ")</f>
+        <f>IF(O34&gt;0,O34-N(R34)-N(AC34)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T34" s="11"/>
@@ -3631,8 +3743,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA34" s="22"/>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB34" s="42"/>
+      <c r="AC34" s="11" t="str">
+        <f>IF(AND(O34&gt;0,AB34="S"),O34*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A35" s="101"/>
       <c r="B35" s="117" t="s">
         <v>70</v>
@@ -3707,8 +3824,13 @@
         <v>0</v>
       </c>
       <c r="AA35" s="22"/>
-    </row>
-    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB35" s="22"/>
+      <c r="AC35" s="17">
+        <f>SUM(AC30:AC34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="101"/>
       <c r="B36" s="37"/>
       <c r="C36" s="76"/>
@@ -3737,7 +3859,7 @@
       <c r="Z36" s="7"/>
       <c r="AA36" s="22"/>
     </row>
-    <row r="37" spans="1:27" ht="13" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:29" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="101"/>
       <c r="B37" s="120" t="s">
         <v>63</v>
@@ -3774,7 +3896,7 @@
       <c r="Z37" s="7"/>
       <c r="AA37" s="22"/>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A38" s="101"/>
       <c r="B38" s="42"/>
       <c r="C38" s="75"/>
@@ -3810,11 +3932,11 @@
       <c r="P38" s="88"/>
       <c r="Q38" s="11"/>
       <c r="R38" s="11" t="str">
-        <f>IF(O38&gt;0,O38*R$4*(1-M38)," ")</f>
+        <f>IF(AND(O38&gt;0,AB38&lt;&gt;"S"),O38*R$4*(1-M38)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S38" s="11" t="str">
-        <f>IF(O38&gt;0,O38-R38," ")</f>
+        <f>IF(O38&gt;0,O38-N(R38)-N(AC38)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T38" s="11"/>
@@ -3837,8 +3959,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA38" s="22"/>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB38" s="42"/>
+      <c r="AC38" s="11" t="str">
+        <f>IF(AND(O38&gt;0,AB38="S"),O38*AC$4*(1-M38)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A39" s="101"/>
       <c r="B39" s="42"/>
       <c r="C39" s="75"/>
@@ -3874,11 +4001,11 @@
       <c r="P39" s="88"/>
       <c r="Q39" s="11"/>
       <c r="R39" s="11" t="str">
-        <f>IF(O39&gt;0,O39*R$4*(1-M39)," ")</f>
+        <f>IF(AND(O39&gt;0,AB39&lt;&gt;"S"),O39*R$4*(1-M39)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S39" s="11" t="str">
-        <f>IF(O39&gt;0,O39-R39," ")</f>
+        <f>IF(O39&gt;0,O39-N(R39)-N(AC39)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T39" s="11"/>
@@ -3901,8 +4028,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA39" s="22"/>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="11" t="str">
+        <f>IF(AND(O39&gt;0,AB39="S"),O39*AC$4*(1-M39)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A40" s="101"/>
       <c r="B40" s="42"/>
       <c r="C40" s="75"/>
@@ -3938,11 +4070,11 @@
       <c r="P40" s="88"/>
       <c r="Q40" s="11"/>
       <c r="R40" s="11" t="str">
-        <f>IF(O40&gt;0,O40*R$4*(1-M40)," ")</f>
+        <f>IF(AND(O40&gt;0,AB40&lt;&gt;"S"),O40*R$4*(1-M40)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S40" s="11" t="str">
-        <f>IF(O40&gt;0,O40-R40," ")</f>
+        <f>IF(O40&gt;0,O40-N(R40)-N(AC40)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T40" s="11"/>
@@ -3965,8 +4097,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA40" s="22"/>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB40" s="42"/>
+      <c r="AC40" s="11" t="str">
+        <f>IF(AND(O40&gt;0,AB40="S"),O40*AC$4*(1-M40)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A41" s="101"/>
       <c r="B41" s="42"/>
       <c r="C41" s="75"/>
@@ -4002,11 +4139,11 @@
       <c r="P41" s="88"/>
       <c r="Q41" s="11"/>
       <c r="R41" s="11" t="str">
-        <f>IF(O41&gt;0,O41*R$4*(1-M41)," ")</f>
+        <f>IF(AND(O41&gt;0,AB41&lt;&gt;"S"),O41*R$4*(1-M41)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S41" s="11" t="str">
-        <f>IF(O41&gt;0,O41-R41," ")</f>
+        <f>IF(O41&gt;0,O41-N(R41)-N(AC41)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T41" s="11"/>
@@ -4029,8 +4166,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA41" s="22"/>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB41" s="42"/>
+      <c r="AC41" s="11" t="str">
+        <f>IF(AND(O41&gt;0,AB41="S"),O41*AC$4*(1-M41)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A42" s="101"/>
       <c r="B42" s="42"/>
       <c r="C42" s="75"/>
@@ -4066,11 +4208,11 @@
       <c r="P42" s="88"/>
       <c r="Q42" s="11"/>
       <c r="R42" s="11" t="str">
-        <f>IF(O42&gt;0,O42*R$4*(1-M42)," ")</f>
+        <f>IF(AND(O42&gt;0,AB42&lt;&gt;"S"),O42*R$4*(1-M42)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S42" s="11" t="str">
-        <f>IF(O42&gt;0,O42-R42," ")</f>
+        <f>IF(O42&gt;0,O42-N(R42)-N(AC42)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T42" s="11"/>
@@ -4093,8 +4235,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA42" s="22"/>
-    </row>
-    <row r="43" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB42" s="42"/>
+      <c r="AC42" s="11" t="str">
+        <f>IF(AND(O42&gt;0,AB42="S"),O42*AC$4*(1-M42)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="101"/>
       <c r="B43" s="120" t="s">
         <v>64</v>
@@ -4128,7 +4275,7 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="22"/>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A44" s="101"/>
       <c r="B44" s="42"/>
       <c r="C44" s="75"/>
@@ -4164,11 +4311,11 @@
       <c r="P44" s="88"/>
       <c r="Q44" s="11"/>
       <c r="R44" s="11" t="str">
-        <f>IF(O44&gt;0,O44*R$4*(1-M44)," ")</f>
+        <f>IF(AND(O44&gt;0,AB44&lt;&gt;"S"),O44*R$4*(1-M44)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S44" s="11" t="str">
-        <f>IF(O44&gt;0,O44-R44," ")</f>
+        <f>IF(O44&gt;0,O44-N(R44)-N(AC44)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T44" s="11"/>
@@ -4191,8 +4338,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA44" s="22"/>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB44" s="42"/>
+      <c r="AC44" s="11" t="str">
+        <f>IF(AND(O44&gt;0,AB44="S"),O44*AC$4*(1-M44)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A45" s="101"/>
       <c r="B45" s="42"/>
       <c r="C45" s="75"/>
@@ -4228,11 +4380,11 @@
       <c r="P45" s="88"/>
       <c r="Q45" s="11"/>
       <c r="R45" s="11" t="str">
-        <f>IF(O45&gt;0,O45*R$4*(1-M45)," ")</f>
+        <f>IF(AND(O45&gt;0,AB45&lt;&gt;"S"),O45*R$4*(1-M45)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S45" s="11" t="str">
-        <f>IF(O45&gt;0,O45-R45," ")</f>
+        <f>IF(O45&gt;0,O45-N(R45)-N(AC45)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T45" s="11"/>
@@ -4255,8 +4407,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA45" s="22"/>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB45" s="42"/>
+      <c r="AC45" s="11" t="str">
+        <f>IF(AND(O45&gt;0,AB45="S"),O45*AC$4*(1-M45)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A46" s="101"/>
       <c r="B46" s="42"/>
       <c r="C46" s="75"/>
@@ -4292,11 +4449,11 @@
       <c r="P46" s="88"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="11" t="str">
-        <f>IF(O46&gt;0,O46*R$4*(1-M46)," ")</f>
+        <f>IF(AND(O46&gt;0,AB46&lt;&gt;"S"),O46*R$4*(1-M46)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S46" s="11" t="str">
-        <f>IF(O46&gt;0,O46-R46," ")</f>
+        <f>IF(O46&gt;0,O46-N(R46)-N(AC46)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T46" s="11"/>
@@ -4319,8 +4476,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA46" s="22"/>
-    </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB46" s="42"/>
+      <c r="AC46" s="11" t="str">
+        <f>IF(AND(O46&gt;0,AB46="S"),O46*AC$4*(1-M46)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A47" s="101"/>
       <c r="B47" s="42"/>
       <c r="C47" s="75"/>
@@ -4356,11 +4518,11 @@
       <c r="P47" s="88"/>
       <c r="Q47" s="11"/>
       <c r="R47" s="11" t="str">
-        <f>IF(O47&gt;0,O47*R$4*(1-M47)," ")</f>
+        <f>IF(AND(O47&gt;0,AB47&lt;&gt;"S"),O47*R$4*(1-M47)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S47" s="11" t="str">
-        <f>IF(O47&gt;0,O47-R47," ")</f>
+        <f>IF(O47&gt;0,O47-N(R47)-N(AC47)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T47" s="11"/>
@@ -4383,8 +4545,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA47" s="22"/>
-    </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB47" s="42"/>
+      <c r="AC47" s="11" t="str">
+        <f>IF(AND(O47&gt;0,AB47="S"),O47*AC$4*(1-M47)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A48" s="101"/>
       <c r="B48" s="42"/>
       <c r="C48" s="75"/>
@@ -4420,11 +4587,11 @@
       <c r="P48" s="88"/>
       <c r="Q48" s="11"/>
       <c r="R48" s="11" t="str">
-        <f>IF(O48&gt;0,O48*R$4*(1-M48)," ")</f>
+        <f>IF(AND(O48&gt;0,AB48&lt;&gt;"S"),O48*R$4*(1-M48)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S48" s="11" t="str">
-        <f>IF(O48&gt;0,O48-R48," ")</f>
+        <f>IF(O48&gt;0,O48-N(R48)-N(AC48)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T48" s="11"/>
@@ -4447,8 +4614,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA48" s="22"/>
-    </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="11" t="str">
+        <f>IF(AND(O48&gt;0,AB48="S"),O48*AC$4*(1-M48)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A49" s="101"/>
       <c r="B49" s="122" t="s">
         <v>54</v>
@@ -4479,7 +4651,7 @@
       <c r="Z49" s="11"/>
       <c r="AA49" s="22"/>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A50" s="101"/>
       <c r="B50" s="42"/>
       <c r="C50" s="75"/>
@@ -4515,11 +4687,11 @@
       <c r="P50" s="88"/>
       <c r="Q50" s="11"/>
       <c r="R50" s="11" t="str">
-        <f>IF(O50&gt;0,O50*R$4," ")</f>
+        <f>IF(AND(O50&gt;0,AB50&lt;&gt;"S"),O50*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S50" s="11" t="str">
-        <f>IF(O50&gt;0,O50-R50," ")</f>
+        <f>IF(O50&gt;0,O50-N(R50)-N(AC50)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T50" s="11"/>
@@ -4542,8 +4714,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA50" s="22"/>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB50" s="42"/>
+      <c r="AC50" s="11" t="str">
+        <f>IF(AND(O50&gt;0,AB50="S"),O50*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A51" s="101"/>
       <c r="B51" s="42"/>
       <c r="C51" s="75"/>
@@ -4579,11 +4756,11 @@
       <c r="P51" s="88"/>
       <c r="Q51" s="11"/>
       <c r="R51" s="11" t="str">
-        <f>IF(O51&gt;0,O51*R$4," ")</f>
+        <f>IF(AND(O51&gt;0,AB51&lt;&gt;"S"),O51*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S51" s="11" t="str">
-        <f>IF(O51&gt;0,O51-R51," ")</f>
+        <f>IF(O51&gt;0,O51-N(R51)-N(AC51)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T51" s="11"/>
@@ -4606,8 +4783,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA51" s="22"/>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB51" s="42"/>
+      <c r="AC51" s="11" t="str">
+        <f>IF(AND(O51&gt;0,AB51="S"),O51*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A52" s="101"/>
       <c r="B52" s="42"/>
       <c r="C52" s="75"/>
@@ -4643,11 +4825,11 @@
       <c r="P52" s="88"/>
       <c r="Q52" s="11"/>
       <c r="R52" s="11" t="str">
-        <f>IF(O52&gt;0,O52*R$4," ")</f>
+        <f>IF(AND(O52&gt;0,AB52&lt;&gt;"S"),O52*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S52" s="11" t="str">
-        <f>IF(O52&gt;0,O52-R52," ")</f>
+        <f>IF(O52&gt;0,O52-N(R52)-N(AC52)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T52" s="11"/>
@@ -4670,8 +4852,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA52" s="22"/>
-    </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB52" s="42"/>
+      <c r="AC52" s="11" t="str">
+        <f>IF(AND(O52&gt;0,AB52="S"),O52*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A53" s="101"/>
       <c r="B53" s="42"/>
       <c r="C53" s="75"/>
@@ -4707,11 +4894,11 @@
       <c r="P53" s="88"/>
       <c r="Q53" s="11"/>
       <c r="R53" s="11" t="str">
-        <f>IF(O53&gt;0,O53*R$4," ")</f>
+        <f>IF(AND(O53&gt;0,AB53&lt;&gt;"S"),O53*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S53" s="11" t="str">
-        <f>IF(O53&gt;0,O53-R53," ")</f>
+        <f>IF(O53&gt;0,O53-N(R53)-N(AC53)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T53" s="11"/>
@@ -4734,8 +4921,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA53" s="22"/>
-    </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB53" s="42"/>
+      <c r="AC53" s="11" t="str">
+        <f>IF(AND(O53&gt;0,AB53="S"),O53*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A54" s="101"/>
       <c r="B54" s="42"/>
       <c r="C54" s="75"/>
@@ -4771,11 +4963,11 @@
       <c r="P54" s="88"/>
       <c r="Q54" s="11"/>
       <c r="R54" s="11" t="str">
-        <f>IF(O54&gt;0,O54*R$4," ")</f>
+        <f>IF(AND(O54&gt;0,AB54&lt;&gt;"S"),O54*R$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S54" s="11" t="str">
-        <f>IF(O54&gt;0,O54-R54," ")</f>
+        <f>IF(O54&gt;0,O54-N(R54)-N(AC54)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T54" s="11"/>
@@ -4798,8 +4990,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA54" s="22"/>
-    </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB54" s="42"/>
+      <c r="AC54" s="11" t="str">
+        <f>IF(AND(O54&gt;0,AB54="S"),O54*AC$4," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A55" s="101"/>
       <c r="B55" s="117" t="s">
         <v>71</v>
@@ -4874,8 +5071,13 @@
         <v>0</v>
       </c>
       <c r="AA55" s="22"/>
-    </row>
-    <row r="56" spans="1:27" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AB55" s="22"/>
+      <c r="AC55" s="17">
+        <f>SUM(AC38:AC54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A56" s="101"/>
       <c r="B56" s="12"/>
       <c r="C56" s="77"/>
@@ -4904,7 +5106,7 @@
       <c r="Z56" s="11"/>
       <c r="AA56" s="22"/>
     </row>
-    <row r="57" spans="1:27" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A57" s="101"/>
       <c r="B57" s="152" t="str">
         <f>B6</f>
@@ -4983,8 +5185,13 @@
         <v>0</v>
       </c>
       <c r="AA57" s="22"/>
-    </row>
-    <row r="58" spans="1:27" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AB57" s="22"/>
+      <c r="AC57" s="19">
+        <f>AC11+AC19+AC27+AC35+AC55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A58" s="101"/>
       <c r="B58" s="14"/>
       <c r="C58" s="78"/>
@@ -5013,7 +5220,7 @@
       <c r="Z58" s="11"/>
       <c r="AA58" s="22"/>
     </row>
-    <row r="59" spans="1:27" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A59" s="101"/>
       <c r="B59" s="152" t="s">
         <v>62</v>
@@ -5047,7 +5254,7 @@
       <c r="Z59" s="11"/>
       <c r="AA59" s="22"/>
     </row>
-    <row r="60" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="101"/>
       <c r="B60" s="122" t="s">
         <v>10</v>
@@ -5081,7 +5288,7 @@
       <c r="Z60" s="11"/>
       <c r="AA60" s="22"/>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A61" s="101"/>
       <c r="B61" s="42"/>
       <c r="C61" s="75"/>
@@ -5128,7 +5335,7 @@
       <c r="Z61" s="11"/>
       <c r="AA61" s="22"/>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A62" s="101"/>
       <c r="B62" s="42"/>
       <c r="C62" s="75"/>
@@ -5175,7 +5382,7 @@
       <c r="Z62" s="11"/>
       <c r="AA62" s="22"/>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A63" s="101"/>
       <c r="B63" s="42"/>
       <c r="C63" s="75"/>
@@ -5222,7 +5429,7 @@
       <c r="Z63" s="11"/>
       <c r="AA63" s="22"/>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A64" s="101"/>
       <c r="B64" s="117" t="s">
         <v>12</v>
@@ -5297,8 +5504,13 @@
         <v>0</v>
       </c>
       <c r="AA64" s="22"/>
-    </row>
-    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB64" s="22"/>
+      <c r="AC64" s="17">
+        <f>SUM(AC61:AC63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="101"/>
       <c r="B65" s="37"/>
       <c r="C65" s="76"/>
@@ -5327,7 +5539,7 @@
       <c r="Z65" s="7"/>
       <c r="AA65" s="22"/>
     </row>
-    <row r="66" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="101"/>
       <c r="B66" s="122" t="s">
         <v>9</v>
@@ -5361,7 +5573,7 @@
       <c r="Z66" s="11"/>
       <c r="AA66" s="22"/>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A67" s="101"/>
       <c r="B67" s="42"/>
       <c r="C67" s="75"/>
@@ -5423,7 +5635,7 @@
       </c>
       <c r="AA67" s="22"/>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A68" s="101"/>
       <c r="B68" s="42"/>
       <c r="C68" s="75"/>
@@ -5485,7 +5697,7 @@
       </c>
       <c r="AA68" s="22"/>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A69" s="101"/>
       <c r="B69" s="42"/>
       <c r="C69" s="75"/>
@@ -5547,7 +5759,7 @@
       </c>
       <c r="AA69" s="22"/>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A70" s="101"/>
       <c r="B70" s="42"/>
       <c r="C70" s="75"/>
@@ -5609,7 +5821,7 @@
       </c>
       <c r="AA70" s="22"/>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A71" s="101"/>
       <c r="B71" s="42"/>
       <c r="C71" s="75"/>
@@ -5671,7 +5883,7 @@
       </c>
       <c r="AA71" s="22"/>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A72" s="101"/>
       <c r="B72" s="117" t="s">
         <v>13</v>
@@ -5746,8 +5958,13 @@
         <v>0</v>
       </c>
       <c r="AA72" s="22"/>
-    </row>
-    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB72" s="22"/>
+      <c r="AC72" s="17">
+        <f>SUM(AC67:AC71)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="101"/>
       <c r="B73" s="37"/>
       <c r="C73" s="76"/>
@@ -5776,7 +5993,7 @@
       <c r="Z73" s="7"/>
       <c r="AA73" s="22"/>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A74" s="101"/>
       <c r="B74" s="122" t="s">
         <v>55</v>
@@ -5810,7 +6027,7 @@
       <c r="Z74" s="11"/>
       <c r="AA74" s="22"/>
     </row>
-    <row r="75" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="101"/>
       <c r="B75" s="42"/>
       <c r="C75" s="75"/>
@@ -5872,7 +6089,7 @@
       </c>
       <c r="AA75" s="22"/>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A76" s="101"/>
       <c r="B76" s="42"/>
       <c r="C76" s="75"/>
@@ -5934,7 +6151,7 @@
       </c>
       <c r="AA76" s="22"/>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A77" s="101"/>
       <c r="B77" s="42"/>
       <c r="C77" s="75"/>
@@ -5996,7 +6213,7 @@
       </c>
       <c r="AA77" s="22"/>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A78" s="101"/>
       <c r="B78" s="42"/>
       <c r="C78" s="75"/>
@@ -6058,7 +6275,7 @@
       </c>
       <c r="AA78" s="22"/>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A79" s="101"/>
       <c r="B79" s="42"/>
       <c r="C79" s="75"/>
@@ -6120,7 +6337,7 @@
       </c>
       <c r="AA79" s="22"/>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A80" s="101"/>
       <c r="B80" s="117" t="s">
         <v>14</v>
@@ -6195,8 +6412,13 @@
         <v>0</v>
       </c>
       <c r="AA80" s="22"/>
-    </row>
-    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB80" s="22"/>
+      <c r="AC80" s="17">
+        <f>SUM(AC75:AC79)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="101"/>
       <c r="B81" s="37"/>
       <c r="C81" s="76"/>
@@ -6225,7 +6447,7 @@
       <c r="Z81" s="7"/>
       <c r="AA81" s="22"/>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A82" s="101"/>
       <c r="B82" s="122" t="s">
         <v>7</v>
@@ -6259,7 +6481,7 @@
       <c r="Z82" s="11"/>
       <c r="AA82" s="22"/>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A83" s="101"/>
       <c r="B83" s="42"/>
       <c r="C83" s="75"/>
@@ -6321,7 +6543,7 @@
       </c>
       <c r="AA83" s="22"/>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A84" s="101"/>
       <c r="B84" s="42"/>
       <c r="C84" s="75"/>
@@ -6383,7 +6605,7 @@
       </c>
       <c r="AA84" s="22"/>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A85" s="101"/>
       <c r="B85" s="42"/>
       <c r="C85" s="75"/>
@@ -6445,7 +6667,7 @@
       </c>
       <c r="AA85" s="22"/>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A86" s="101"/>
       <c r="B86" s="42"/>
       <c r="C86" s="75"/>
@@ -6507,7 +6729,7 @@
       </c>
       <c r="AA86" s="22"/>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A87" s="101"/>
       <c r="B87" s="42"/>
       <c r="C87" s="75"/>
@@ -6569,7 +6791,7 @@
       </c>
       <c r="AA87" s="22"/>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A88" s="101"/>
       <c r="B88" s="117" t="s">
         <v>15</v>
@@ -6644,8 +6866,13 @@
         <v>0</v>
       </c>
       <c r="AA88" s="22"/>
-    </row>
-    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB88" s="22"/>
+      <c r="AC88" s="17">
+        <f>SUM(AC83:AC87)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="101"/>
       <c r="B89" s="37"/>
       <c r="C89" s="76"/>
@@ -6674,7 +6901,7 @@
       <c r="Z89" s="7"/>
       <c r="AA89" s="22"/>
     </row>
-    <row r="90" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="101"/>
       <c r="B90" s="120" t="str">
         <f>B37</f>
@@ -6712,7 +6939,7 @@
       <c r="Z90" s="11"/>
       <c r="AA90" s="22"/>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A91" s="101"/>
       <c r="B91" s="42"/>
       <c r="C91" s="75"/>
@@ -6745,11 +6972,11 @@
       <c r="P91" s="88"/>
       <c r="Q91" s="11"/>
       <c r="R91" s="11" t="str">
-        <f>IF(E91&gt;0,E91*R$4*(1-M91)," ")</f>
+        <f>IF(AND(E91&gt;0,AB91&lt;&gt;"S"),E91*R$4*(1-M91)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S91" s="11" t="str">
-        <f>IF(E91&gt;0,E91-R91," ")</f>
+        <f>IF(E91&gt;0,E91-N(R91)-N(AC91)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T91" s="11"/>
@@ -6772,8 +6999,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA91" s="22"/>
-    </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB91" s="42"/>
+      <c r="AC91" s="11" t="str">
+        <f>IF(AND(E91&gt;0,AB91="S"),E91*AC$4*(1-M91)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A92" s="101"/>
       <c r="B92" s="42"/>
       <c r="C92" s="75"/>
@@ -6806,11 +7038,11 @@
       <c r="P92" s="88"/>
       <c r="Q92" s="11"/>
       <c r="R92" s="11" t="str">
-        <f>IF(E92&gt;0,E92*R$4*(1-M92)," ")</f>
+        <f>IF(AND(E92&gt;0,AB92&lt;&gt;"S"),E92*R$4*(1-M92)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S92" s="11" t="str">
-        <f>IF(E92&gt;0,E92-R92," ")</f>
+        <f>IF(E92&gt;0,E92-N(R92)-N(AC92)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T92" s="11"/>
@@ -6833,8 +7065,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA92" s="22"/>
-    </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB92" s="42"/>
+      <c r="AC92" s="11" t="str">
+        <f>IF(AND(E92&gt;0,AB92="S"),E92*AC$4*(1-M92)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A93" s="101"/>
       <c r="B93" s="42"/>
       <c r="C93" s="75"/>
@@ -6867,11 +7104,11 @@
       <c r="P93" s="88"/>
       <c r="Q93" s="11"/>
       <c r="R93" s="11" t="str">
-        <f>IF(E93&gt;0,E93*R$4*(1-M93)," ")</f>
+        <f>IF(AND(E93&gt;0,AB93&lt;&gt;"S"),E93*R$4*(1-M93)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S93" s="11" t="str">
-        <f>IF(E93&gt;0,E93-R93," ")</f>
+        <f>IF(E93&gt;0,E93-N(R93)-N(AC93)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T93" s="11"/>
@@ -6894,8 +7131,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA93" s="22"/>
-    </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB93" s="42"/>
+      <c r="AC93" s="11" t="str">
+        <f>IF(AND(E93&gt;0,AB93="S"),E93*AC$4*(1-M93)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A94" s="101"/>
       <c r="B94" s="42"/>
       <c r="C94" s="75"/>
@@ -6928,11 +7170,11 @@
       <c r="P94" s="88"/>
       <c r="Q94" s="11"/>
       <c r="R94" s="11" t="str">
-        <f>IF(E94&gt;0,E94*R$4*(1-M94)," ")</f>
+        <f>IF(AND(E94&gt;0,AB94&lt;&gt;"S"),E94*R$4*(1-M94)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S94" s="11" t="str">
-        <f>IF(E94&gt;0,E94-R94," ")</f>
+        <f>IF(E94&gt;0,E94-N(R94)-N(AC94)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T94" s="11"/>
@@ -6955,8 +7197,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA94" s="22"/>
-    </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB94" s="42"/>
+      <c r="AC94" s="11" t="str">
+        <f>IF(AND(E94&gt;0,AB94="S"),E94*AC$4*(1-M94)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A95" s="101"/>
       <c r="B95" s="42"/>
       <c r="C95" s="75"/>
@@ -6989,11 +7236,11 @@
       <c r="P95" s="88"/>
       <c r="Q95" s="11"/>
       <c r="R95" s="11" t="str">
-        <f>IF(E95&gt;0,E95*R$4*(1-M95)," ")</f>
+        <f>IF(AND(E95&gt;0,AB95&lt;&gt;"S"),E95*R$4*(1-M95)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S95" s="11" t="str">
-        <f>IF(E95&gt;0,E95-R95," ")</f>
+        <f>IF(E95&gt;0,E95-N(R95)-N(AC95)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T95" s="11"/>
@@ -7016,8 +7263,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA95" s="22"/>
-    </row>
-    <row r="96" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB95" s="42"/>
+      <c r="AC95" s="11" t="str">
+        <f>IF(AND(E95&gt;0,AB95="S"),E95*AC$4*(1-M95)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="101"/>
       <c r="B96" s="155" t="str">
         <f>B43</f>
@@ -7052,7 +7304,7 @@
       <c r="Z96" s="11"/>
       <c r="AA96" s="22"/>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A97" s="101"/>
       <c r="B97" s="42"/>
       <c r="C97" s="75"/>
@@ -7085,11 +7337,11 @@
       <c r="P97" s="88"/>
       <c r="Q97" s="11"/>
       <c r="R97" s="11" t="str">
-        <f>IF(E97&gt;0,E97*R$4*(1-M97)," ")</f>
+        <f>IF(AND(E97&gt;0,AB97&lt;&gt;"S"),E97*R$4*(1-M97)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S97" s="11" t="str">
-        <f>IF(E97&gt;0,E97-R97," ")</f>
+        <f>IF(E97&gt;0,E97-N(R97)-N(AC97)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T97" s="11"/>
@@ -7112,8 +7364,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA97" s="22"/>
-    </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB97" s="42"/>
+      <c r="AC97" s="11" t="str">
+        <f>IF(AND(E97&gt;0,AB97="S"),E97*AC$4*(1-M97)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A98" s="101"/>
       <c r="B98" s="42"/>
       <c r="C98" s="75"/>
@@ -7146,11 +7403,11 @@
       <c r="P98" s="88"/>
       <c r="Q98" s="11"/>
       <c r="R98" s="11" t="str">
-        <f>IF(E98&gt;0,E98*R$4*(1-M98)," ")</f>
+        <f>IF(AND(E98&gt;0,AB98&lt;&gt;"S"),E98*R$4*(1-M98)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S98" s="11" t="str">
-        <f>IF(E98&gt;0,E98-R98," ")</f>
+        <f>IF(E98&gt;0,E98-N(R98)-N(AC98)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T98" s="11"/>
@@ -7173,8 +7430,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA98" s="22"/>
-    </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB98" s="42"/>
+      <c r="AC98" s="11" t="str">
+        <f>IF(AND(E98&gt;0,AB98="S"),E98*AC$4*(1-M98)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A99" s="101"/>
       <c r="B99" s="42"/>
       <c r="C99" s="75"/>
@@ -7207,11 +7469,11 @@
       <c r="P99" s="88"/>
       <c r="Q99" s="11"/>
       <c r="R99" s="11" t="str">
-        <f>IF(E99&gt;0,E99*R$4*(1-M99)," ")</f>
+        <f>IF(AND(E99&gt;0,AB99&lt;&gt;"S"),E99*R$4*(1-M99)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S99" s="11" t="str">
-        <f>IF(E99&gt;0,E99-R99," ")</f>
+        <f>IF(E99&gt;0,E99-N(R99)-N(AC99)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T99" s="11"/>
@@ -7234,8 +7496,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA99" s="22"/>
-    </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB99" s="42"/>
+      <c r="AC99" s="11" t="str">
+        <f>IF(AND(E99&gt;0,AB99="S"),E99*AC$4*(1-M99)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A100" s="101"/>
       <c r="B100" s="42"/>
       <c r="C100" s="75"/>
@@ -7268,11 +7535,11 @@
       <c r="P100" s="88"/>
       <c r="Q100" s="11"/>
       <c r="R100" s="11" t="str">
-        <f>IF(E100&gt;0,E100*R$4*(1-M100)," ")</f>
+        <f>IF(AND(E100&gt;0,AB100&lt;&gt;"S"),E100*R$4*(1-M100)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S100" s="11" t="str">
-        <f>IF(E100&gt;0,E100-R100," ")</f>
+        <f>IF(E100&gt;0,E100-N(R100)-N(AC100)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T100" s="11"/>
@@ -7295,8 +7562,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA100" s="22"/>
-    </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB100" s="42"/>
+      <c r="AC100" s="11" t="str">
+        <f>IF(AND(E100&gt;0,AB100="S"),E100*AC$4*(1-M100)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A101" s="101"/>
       <c r="B101" s="42"/>
       <c r="C101" s="75"/>
@@ -7329,11 +7601,11 @@
       <c r="P101" s="88"/>
       <c r="Q101" s="11"/>
       <c r="R101" s="11" t="str">
-        <f>IF(E101&gt;0,E101*R$4*(1-M101)," ")</f>
+        <f>IF(AND(E101&gt;0,AB101&lt;&gt;"S"),E101*R$4*(1-M101)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S101" s="11" t="str">
-        <f>IF(E101&gt;0,E101-R101," ")</f>
+        <f>IF(E101&gt;0,E101-N(R101)-N(AC101)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="T101" s="11"/>
@@ -7356,8 +7628,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA101" s="22"/>
-    </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="AB101" s="42"/>
+      <c r="AC101" s="11" t="str">
+        <f>IF(AND(E101&gt;0,AB101="S"),E101*AC$4*(1-M101)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="102" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A102" s="101"/>
       <c r="B102" s="122" t="s">
         <v>54</v>
@@ -7388,7 +7665,7 @@
       <c r="Z102" s="11"/>
       <c r="AA102" s="22"/>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A103" s="101"/>
       <c r="B103" s="42"/>
       <c r="C103" s="75"/>
@@ -7452,7 +7729,7 @@
       </c>
       <c r="AA103" s="22"/>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A104" s="101"/>
       <c r="B104" s="42"/>
       <c r="C104" s="75"/>
@@ -7516,7 +7793,7 @@
       </c>
       <c r="AA104" s="22"/>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A105" s="101"/>
       <c r="B105" s="42"/>
       <c r="C105" s="75"/>
@@ -7580,7 +7857,7 @@
       </c>
       <c r="AA105" s="22"/>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A106" s="101"/>
       <c r="B106" s="42"/>
       <c r="C106" s="75"/>
@@ -7644,7 +7921,7 @@
       </c>
       <c r="AA106" s="22"/>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A107" s="101"/>
       <c r="B107" s="42"/>
       <c r="C107" s="75"/>
@@ -7708,7 +7985,7 @@
       </c>
       <c r="AA107" s="22"/>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A108" s="101"/>
       <c r="B108" s="117" t="s">
         <v>16</v>
@@ -7783,8 +8060,13 @@
         <v>0</v>
       </c>
       <c r="AA108" s="22"/>
-    </row>
-    <row r="109" spans="1:27" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AB108" s="22"/>
+      <c r="AC108" s="17">
+        <f>SUM(AC91:AC107)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:29" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A109" s="101"/>
       <c r="B109" s="12"/>
       <c r="C109" s="77"/>
@@ -7813,7 +8095,7 @@
       <c r="Z109" s="11"/>
       <c r="AA109" s="22"/>
     </row>
-    <row r="110" spans="1:27" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:29" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A110" s="101"/>
       <c r="B110" s="152" t="str">
         <f>B59</f>
@@ -7892,8 +8174,13 @@
         <v>0</v>
       </c>
       <c r="AA110" s="22"/>
-    </row>
-    <row r="111" spans="1:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AB110" s="22"/>
+      <c r="AC110" s="19">
+        <f>AC64+AC72+AC80+AC88+AC108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:29" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A111" s="102"/>
       <c r="B111" s="24"/>
       <c r="C111" s="79"/>

--- a/packages/GB Accounts Self Employed 2023-04-05 (Apr23) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Self Employed 2023-04-05 (Apr23) Excel 2007/Fixedassets.xlsx
@@ -1781,7 +1781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC111"/>
+  <dimension ref="A1:AG111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="5" customWidth="1"/>
@@ -1809,12 +1809,14 @@
     <col min="24" max="24" width="11.33203125" style="3" customWidth="1"/>
     <col min="25" max="26" width="9.1640625" style="2"/>
     <col min="27" max="27" width="1.6640625" style="5" customWidth="1"/>
-    <col min="28" max="16384" width="9.1640625" style="5"/>
     <col min="28" max="28" width="5.6640625" style="89" customWidth="1"/>
     <col min="29" max="29" width="10.6640625" style="2" customWidth="1"/>
+    <col min="30" max="30" width="5.6640625" style="89" customWidth="1"/>
+    <col min="31" max="33" width="10.6640625" style="2" customWidth="1"/>
+    <col min="34" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:33" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="123"/>
       <c r="B1" s="134" t="s">
         <v>0</v>
@@ -1904,8 +1906,17 @@
         <f>AC57+AC110</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE1" s="20">
+        <f>AE57+AE110</f>
+      </c>
+      <c r="AF1" s="20">
+        <f>AF57+AF110</f>
+      </c>
+      <c r="AG1" s="20">
+        <f>AG57+AG110</f>
+      </c>
+    </row>
+    <row r="2" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="124"/>
       <c r="B2" s="134"/>
       <c r="C2" s="135" t="s">
@@ -1977,8 +1988,28 @@
           <t>Special Rate W Down Allowance</t>
         </is>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AD2" s="130" t="inlineStr">
+        <is>
+          <t>Single asset pool (P = private use or short-life asset)</t>
+        </is>
+      </c>
+      <c r="AE2" s="132" t="inlineStr">
+        <is>
+          <t>Single Asset Pool W Down Allowance main rate</t>
+        </is>
+      </c>
+      <c r="AF2" s="132" t="inlineStr">
+        <is>
+          <t>Single Asset Pool W Down Allowance special rate</t>
+        </is>
+      </c>
+      <c r="AG2" s="132" t="inlineStr">
+        <is>
+          <t>Single Asset Pool Written Down Tax Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="124"/>
       <c r="B3" s="134"/>
       <c r="C3" s="136"/>
@@ -2007,7 +2038,7 @@
       <c r="Z3" s="132"/>
       <c r="AA3" s="22"/>
     </row>
-    <row r="4" spans="1:29" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:33" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="124"/>
       <c r="B4" s="134"/>
       <c r="C4" s="136"/>
@@ -2065,7 +2096,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="16" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" s="16" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="100"/>
       <c r="B5" s="55"/>
       <c r="C5" s="74"/>
@@ -2094,7 +2125,7 @@
       <c r="Z5" s="57"/>
       <c r="AA5" s="23"/>
     </row>
-    <row r="6" spans="1:29" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="101"/>
       <c r="B6" s="152" t="s">
         <v>61</v>
@@ -2128,7 +2159,7 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:33" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="101"/>
       <c r="B7" s="122" t="s">
         <v>10</v>
@@ -2162,7 +2193,7 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="22"/>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A8" s="101"/>
       <c r="B8" s="42"/>
       <c r="C8" s="75"/>
@@ -2212,7 +2243,7 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="22"/>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A9" s="101"/>
       <c r="B9" s="42"/>
       <c r="C9" s="75"/>
@@ -2262,7 +2293,7 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="22"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A10" s="101"/>
       <c r="B10" s="42"/>
       <c r="C10" s="75"/>
@@ -2312,7 +2343,7 @@
       <c r="Z10" s="11"/>
       <c r="AA10" s="22"/>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A11" s="101"/>
       <c r="B11" s="117" t="s">
         <v>67</v>
@@ -2392,8 +2423,17 @@
         <f>SUM(AC8:AC10)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE11" s="17">
+        <f>SUM(AE8:AE10)</f>
+      </c>
+      <c r="AF11" s="17">
+        <f>SUM(AF8:AF10)</f>
+      </c>
+      <c r="AG11" s="17">
+        <f>SUM(AG8:AG10)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="101"/>
       <c r="B12" s="37"/>
       <c r="C12" s="76"/>
@@ -2422,7 +2462,7 @@
       <c r="Z12" s="7"/>
       <c r="AA12" s="22"/>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A13" s="101"/>
       <c r="B13" s="122" t="s">
         <v>9</v>
@@ -2456,7 +2496,7 @@
       <c r="Z13" s="11"/>
       <c r="AA13" s="22"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A14" s="101"/>
       <c r="B14" s="42"/>
       <c r="C14" s="75"/>
@@ -2522,8 +2562,17 @@
         <f>IF(AND(O14&gt;0,AB14="S"),O14*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE14" s="11" t="str">
+        <f>IF(AND(AD14="P",AB14&lt;&gt;"S"),N(R14)," ")</f>
+      </c>
+      <c r="AF14" s="11" t="str">
+        <f>IF(AND(AD14="P",AB14="S"),N(AC14)," ")</f>
+      </c>
+      <c r="AG14" s="11" t="str">
+        <f>IF(AD14="P",N(S14)," ")</f>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A15" s="101"/>
       <c r="B15" s="42"/>
       <c r="C15" s="75"/>
@@ -2589,8 +2638,17 @@
         <f>IF(AND(O15&gt;0,AB15="S"),O15*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE15" s="11" t="str">
+        <f>IF(AND(AD15="P",AB15&lt;&gt;"S"),N(R15)," ")</f>
+      </c>
+      <c r="AF15" s="11" t="str">
+        <f>IF(AND(AD15="P",AB15="S"),N(AC15)," ")</f>
+      </c>
+      <c r="AG15" s="11" t="str">
+        <f>IF(AD15="P",N(S15)," ")</f>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A16" s="101"/>
       <c r="B16" s="42"/>
       <c r="C16" s="75"/>
@@ -2656,8 +2714,17 @@
         <f>IF(AND(O16&gt;0,AB16="S"),O16*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE16" s="11" t="str">
+        <f>IF(AND(AD16="P",AB16&lt;&gt;"S"),N(R16)," ")</f>
+      </c>
+      <c r="AF16" s="11" t="str">
+        <f>IF(AND(AD16="P",AB16="S"),N(AC16)," ")</f>
+      </c>
+      <c r="AG16" s="11" t="str">
+        <f>IF(AD16="P",N(S16)," ")</f>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A17" s="101"/>
       <c r="B17" s="42"/>
       <c r="C17" s="75"/>
@@ -2723,8 +2790,17 @@
         <f>IF(AND(O17&gt;0,AB17="S"),O17*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE17" s="11" t="str">
+        <f>IF(AND(AD17="P",AB17&lt;&gt;"S"),N(R17)," ")</f>
+      </c>
+      <c r="AF17" s="11" t="str">
+        <f>IF(AND(AD17="P",AB17="S"),N(AC17)," ")</f>
+      </c>
+      <c r="AG17" s="11" t="str">
+        <f>IF(AD17="P",N(S17)," ")</f>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A18" s="101"/>
       <c r="B18" s="42"/>
       <c r="C18" s="75"/>
@@ -2790,8 +2866,17 @@
         <f>IF(AND(O18&gt;0,AB18="S"),O18*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE18" s="11" t="str">
+        <f>IF(AND(AD18="P",AB18&lt;&gt;"S"),N(R18)," ")</f>
+      </c>
+      <c r="AF18" s="11" t="str">
+        <f>IF(AND(AD18="P",AB18="S"),N(AC18)," ")</f>
+      </c>
+      <c r="AG18" s="11" t="str">
+        <f>IF(AD18="P",N(S18)," ")</f>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A19" s="101"/>
       <c r="B19" s="117" t="s">
         <v>68</v>
@@ -2871,8 +2956,17 @@
         <f>SUM(AC14:AC18)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE19" s="17">
+        <f>SUM(AE14:AE18)</f>
+      </c>
+      <c r="AF19" s="17">
+        <f>SUM(AF14:AF18)</f>
+      </c>
+      <c r="AG19" s="17">
+        <f>SUM(AG14:AG18)</f>
+      </c>
+    </row>
+    <row r="20" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="101"/>
       <c r="B20" s="37"/>
       <c r="C20" s="76"/>
@@ -2901,7 +2995,7 @@
       <c r="Z20" s="7"/>
       <c r="AA20" s="22"/>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A21" s="101"/>
       <c r="B21" s="122" t="s">
         <v>55</v>
@@ -2935,7 +3029,7 @@
       <c r="Z21" s="11"/>
       <c r="AA21" s="22"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A22" s="101"/>
       <c r="B22" s="42"/>
       <c r="C22" s="75"/>
@@ -3001,8 +3095,17 @@
         <f>IF(AND(O22&gt;0,AB22="S"),O22*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE22" s="11" t="str">
+        <f>IF(AND(AD22="P",AB22&lt;&gt;"S"),N(R22)," ")</f>
+      </c>
+      <c r="AF22" s="11" t="str">
+        <f>IF(AND(AD22="P",AB22="S"),N(AC22)," ")</f>
+      </c>
+      <c r="AG22" s="11" t="str">
+        <f>IF(AD22="P",N(S22)," ")</f>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A23" s="101"/>
       <c r="B23" s="42"/>
       <c r="C23" s="75"/>
@@ -3068,8 +3171,17 @@
         <f>IF(AND(O23&gt;0,AB23="S"),O23*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE23" s="11" t="str">
+        <f>IF(AND(AD23="P",AB23&lt;&gt;"S"),N(R23)," ")</f>
+      </c>
+      <c r="AF23" s="11" t="str">
+        <f>IF(AND(AD23="P",AB23="S"),N(AC23)," ")</f>
+      </c>
+      <c r="AG23" s="11" t="str">
+        <f>IF(AD23="P",N(S23)," ")</f>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A24" s="101"/>
       <c r="B24" s="42"/>
       <c r="C24" s="75"/>
@@ -3135,8 +3247,17 @@
         <f>IF(AND(O24&gt;0,AB24="S"),O24*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE24" s="11" t="str">
+        <f>IF(AND(AD24="P",AB24&lt;&gt;"S"),N(R24)," ")</f>
+      </c>
+      <c r="AF24" s="11" t="str">
+        <f>IF(AND(AD24="P",AB24="S"),N(AC24)," ")</f>
+      </c>
+      <c r="AG24" s="11" t="str">
+        <f>IF(AD24="P",N(S24)," ")</f>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A25" s="101"/>
       <c r="B25" s="42"/>
       <c r="C25" s="75"/>
@@ -3202,8 +3323,17 @@
         <f>IF(AND(O25&gt;0,AB25="S"),O25*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE25" s="11" t="str">
+        <f>IF(AND(AD25="P",AB25&lt;&gt;"S"),N(R25)," ")</f>
+      </c>
+      <c r="AF25" s="11" t="str">
+        <f>IF(AND(AD25="P",AB25="S"),N(AC25)," ")</f>
+      </c>
+      <c r="AG25" s="11" t="str">
+        <f>IF(AD25="P",N(S25)," ")</f>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A26" s="101"/>
       <c r="B26" s="42"/>
       <c r="C26" s="75"/>
@@ -3269,8 +3399,17 @@
         <f>IF(AND(O26&gt;0,AB26="S"),O26*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE26" s="11" t="str">
+        <f>IF(AND(AD26="P",AB26&lt;&gt;"S"),N(R26)," ")</f>
+      </c>
+      <c r="AF26" s="11" t="str">
+        <f>IF(AND(AD26="P",AB26="S"),N(AC26)," ")</f>
+      </c>
+      <c r="AG26" s="11" t="str">
+        <f>IF(AD26="P",N(S26)," ")</f>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A27" s="101"/>
       <c r="B27" s="117" t="s">
         <v>69</v>
@@ -3350,8 +3489,17 @@
         <f>SUM(AC22:AC26)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE27" s="17">
+        <f>SUM(AE22:AE26)</f>
+      </c>
+      <c r="AF27" s="17">
+        <f>SUM(AF22:AF26)</f>
+      </c>
+      <c r="AG27" s="17">
+        <f>SUM(AG22:AG26)</f>
+      </c>
+    </row>
+    <row r="28" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="101"/>
       <c r="B28" s="37"/>
       <c r="C28" s="76"/>
@@ -3380,7 +3528,7 @@
       <c r="Z28" s="7"/>
       <c r="AA28" s="22"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A29" s="101"/>
       <c r="B29" s="122" t="s">
         <v>7</v>
@@ -3414,7 +3562,7 @@
       <c r="Z29" s="11"/>
       <c r="AA29" s="22"/>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A30" s="101"/>
       <c r="B30" s="42"/>
       <c r="C30" s="75"/>
@@ -3480,8 +3628,17 @@
         <f>IF(AND(O30&gt;0,AB30="S"),O30*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE30" s="11" t="str">
+        <f>IF(AND(AD30="P",AB30&lt;&gt;"S"),N(R30)," ")</f>
+      </c>
+      <c r="AF30" s="11" t="str">
+        <f>IF(AND(AD30="P",AB30="S"),N(AC30)," ")</f>
+      </c>
+      <c r="AG30" s="11" t="str">
+        <f>IF(AD30="P",N(S30)," ")</f>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A31" s="101"/>
       <c r="B31" s="42"/>
       <c r="C31" s="75"/>
@@ -3547,8 +3704,17 @@
         <f>IF(AND(O31&gt;0,AB31="S"),O31*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE31" s="11" t="str">
+        <f>IF(AND(AD31="P",AB31&lt;&gt;"S"),N(R31)," ")</f>
+      </c>
+      <c r="AF31" s="11" t="str">
+        <f>IF(AND(AD31="P",AB31="S"),N(AC31)," ")</f>
+      </c>
+      <c r="AG31" s="11" t="str">
+        <f>IF(AD31="P",N(S31)," ")</f>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A32" s="101"/>
       <c r="B32" s="42"/>
       <c r="C32" s="75"/>
@@ -3614,8 +3780,17 @@
         <f>IF(AND(O32&gt;0,AB32="S"),O32*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE32" s="11" t="str">
+        <f>IF(AND(AD32="P",AB32&lt;&gt;"S"),N(R32)," ")</f>
+      </c>
+      <c r="AF32" s="11" t="str">
+        <f>IF(AND(AD32="P",AB32="S"),N(AC32)," ")</f>
+      </c>
+      <c r="AG32" s="11" t="str">
+        <f>IF(AD32="P",N(S32)," ")</f>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A33" s="101"/>
       <c r="B33" s="42"/>
       <c r="C33" s="75"/>
@@ -3681,8 +3856,17 @@
         <f>IF(AND(O33&gt;0,AB33="S"),O33*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE33" s="11" t="str">
+        <f>IF(AND(AD33="P",AB33&lt;&gt;"S"),N(R33)," ")</f>
+      </c>
+      <c r="AF33" s="11" t="str">
+        <f>IF(AND(AD33="P",AB33="S"),N(AC33)," ")</f>
+      </c>
+      <c r="AG33" s="11" t="str">
+        <f>IF(AD33="P",N(S33)," ")</f>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A34" s="101"/>
       <c r="B34" s="42"/>
       <c r="C34" s="75"/>
@@ -3748,8 +3932,17 @@
         <f>IF(AND(O34&gt;0,AB34="S"),O34*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE34" s="11" t="str">
+        <f>IF(AND(AD34="P",AB34&lt;&gt;"S"),N(R34)," ")</f>
+      </c>
+      <c r="AF34" s="11" t="str">
+        <f>IF(AND(AD34="P",AB34="S"),N(AC34)," ")</f>
+      </c>
+      <c r="AG34" s="11" t="str">
+        <f>IF(AD34="P",N(S34)," ")</f>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A35" s="101"/>
       <c r="B35" s="117" t="s">
         <v>70</v>
@@ -3829,8 +4022,17 @@
         <f>SUM(AC30:AC34)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE35" s="17">
+        <f>SUM(AE30:AE34)</f>
+      </c>
+      <c r="AF35" s="17">
+        <f>SUM(AF30:AF34)</f>
+      </c>
+      <c r="AG35" s="17">
+        <f>SUM(AG30:AG34)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="101"/>
       <c r="B36" s="37"/>
       <c r="C36" s="76"/>
@@ -3859,7 +4061,7 @@
       <c r="Z36" s="7"/>
       <c r="AA36" s="22"/>
     </row>
-    <row r="37" spans="1:29" ht="13" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:33" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="101"/>
       <c r="B37" s="120" t="s">
         <v>63</v>
@@ -3896,7 +4098,7 @@
       <c r="Z37" s="7"/>
       <c r="AA37" s="22"/>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A38" s="101"/>
       <c r="B38" s="42"/>
       <c r="C38" s="75"/>
@@ -3964,8 +4166,17 @@
         <f>IF(AND(O38&gt;0,AB38="S"),O38*AC$4*(1-M38)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE38" s="11" t="str">
+        <f>IF(AND(AD38="P",AB38&lt;&gt;"S"),N(R38)," ")</f>
+      </c>
+      <c r="AF38" s="11" t="str">
+        <f>IF(AND(AD38="P",AB38="S"),N(AC38)," ")</f>
+      </c>
+      <c r="AG38" s="11" t="str">
+        <f>IF(AD38="P",N(S38)," ")</f>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A39" s="101"/>
       <c r="B39" s="42"/>
       <c r="C39" s="75"/>
@@ -4033,8 +4244,17 @@
         <f>IF(AND(O39&gt;0,AB39="S"),O39*AC$4*(1-M39)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE39" s="11" t="str">
+        <f>IF(AND(AD39="P",AB39&lt;&gt;"S"),N(R39)," ")</f>
+      </c>
+      <c r="AF39" s="11" t="str">
+        <f>IF(AND(AD39="P",AB39="S"),N(AC39)," ")</f>
+      </c>
+      <c r="AG39" s="11" t="str">
+        <f>IF(AD39="P",N(S39)," ")</f>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A40" s="101"/>
       <c r="B40" s="42"/>
       <c r="C40" s="75"/>
@@ -4102,8 +4322,17 @@
         <f>IF(AND(O40&gt;0,AB40="S"),O40*AC$4*(1-M40)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE40" s="11" t="str">
+        <f>IF(AND(AD40="P",AB40&lt;&gt;"S"),N(R40)," ")</f>
+      </c>
+      <c r="AF40" s="11" t="str">
+        <f>IF(AND(AD40="P",AB40="S"),N(AC40)," ")</f>
+      </c>
+      <c r="AG40" s="11" t="str">
+        <f>IF(AD40="P",N(S40)," ")</f>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A41" s="101"/>
       <c r="B41" s="42"/>
       <c r="C41" s="75"/>
@@ -4171,8 +4400,17 @@
         <f>IF(AND(O41&gt;0,AB41="S"),O41*AC$4*(1-M41)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE41" s="11" t="str">
+        <f>IF(AND(AD41="P",AB41&lt;&gt;"S"),N(R41)," ")</f>
+      </c>
+      <c r="AF41" s="11" t="str">
+        <f>IF(AND(AD41="P",AB41="S"),N(AC41)," ")</f>
+      </c>
+      <c r="AG41" s="11" t="str">
+        <f>IF(AD41="P",N(S41)," ")</f>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A42" s="101"/>
       <c r="B42" s="42"/>
       <c r="C42" s="75"/>
@@ -4240,8 +4478,17 @@
         <f>IF(AND(O42&gt;0,AB42="S"),O42*AC$4*(1-M42)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="43" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE42" s="11" t="str">
+        <f>IF(AND(AD42="P",AB42&lt;&gt;"S"),N(R42)," ")</f>
+      </c>
+      <c r="AF42" s="11" t="str">
+        <f>IF(AND(AD42="P",AB42="S"),N(AC42)," ")</f>
+      </c>
+      <c r="AG42" s="11" t="str">
+        <f>IF(AD42="P",N(S42)," ")</f>
+      </c>
+    </row>
+    <row r="43" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="101"/>
       <c r="B43" s="120" t="s">
         <v>64</v>
@@ -4275,7 +4522,7 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="22"/>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A44" s="101"/>
       <c r="B44" s="42"/>
       <c r="C44" s="75"/>
@@ -4343,8 +4590,17 @@
         <f>IF(AND(O44&gt;0,AB44="S"),O44*AC$4*(1-M44)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE44" s="11" t="str">
+        <f>IF(AND(AD44="P",AB44&lt;&gt;"S"),N(R44)," ")</f>
+      </c>
+      <c r="AF44" s="11" t="str">
+        <f>IF(AND(AD44="P",AB44="S"),N(AC44)," ")</f>
+      </c>
+      <c r="AG44" s="11" t="str">
+        <f>IF(AD44="P",N(S44)," ")</f>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A45" s="101"/>
       <c r="B45" s="42"/>
       <c r="C45" s="75"/>
@@ -4412,8 +4668,17 @@
         <f>IF(AND(O45&gt;0,AB45="S"),O45*AC$4*(1-M45)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE45" s="11" t="str">
+        <f>IF(AND(AD45="P",AB45&lt;&gt;"S"),N(R45)," ")</f>
+      </c>
+      <c r="AF45" s="11" t="str">
+        <f>IF(AND(AD45="P",AB45="S"),N(AC45)," ")</f>
+      </c>
+      <c r="AG45" s="11" t="str">
+        <f>IF(AD45="P",N(S45)," ")</f>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A46" s="101"/>
       <c r="B46" s="42"/>
       <c r="C46" s="75"/>
@@ -4481,8 +4746,17 @@
         <f>IF(AND(O46&gt;0,AB46="S"),O46*AC$4*(1-M46)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE46" s="11" t="str">
+        <f>IF(AND(AD46="P",AB46&lt;&gt;"S"),N(R46)," ")</f>
+      </c>
+      <c r="AF46" s="11" t="str">
+        <f>IF(AND(AD46="P",AB46="S"),N(AC46)," ")</f>
+      </c>
+      <c r="AG46" s="11" t="str">
+        <f>IF(AD46="P",N(S46)," ")</f>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A47" s="101"/>
       <c r="B47" s="42"/>
       <c r="C47" s="75"/>
@@ -4550,8 +4824,17 @@
         <f>IF(AND(O47&gt;0,AB47="S"),O47*AC$4*(1-M47)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE47" s="11" t="str">
+        <f>IF(AND(AD47="P",AB47&lt;&gt;"S"),N(R47)," ")</f>
+      </c>
+      <c r="AF47" s="11" t="str">
+        <f>IF(AND(AD47="P",AB47="S"),N(AC47)," ")</f>
+      </c>
+      <c r="AG47" s="11" t="str">
+        <f>IF(AD47="P",N(S47)," ")</f>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A48" s="101"/>
       <c r="B48" s="42"/>
       <c r="C48" s="75"/>
@@ -4619,8 +4902,17 @@
         <f>IF(AND(O48&gt;0,AB48="S"),O48*AC$4*(1-M48)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE48" s="11" t="str">
+        <f>IF(AND(AD48="P",AB48&lt;&gt;"S"),N(R48)," ")</f>
+      </c>
+      <c r="AF48" s="11" t="str">
+        <f>IF(AND(AD48="P",AB48="S"),N(AC48)," ")</f>
+      </c>
+      <c r="AG48" s="11" t="str">
+        <f>IF(AD48="P",N(S48)," ")</f>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A49" s="101"/>
       <c r="B49" s="122" t="s">
         <v>54</v>
@@ -4651,7 +4943,7 @@
       <c r="Z49" s="11"/>
       <c r="AA49" s="22"/>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A50" s="101"/>
       <c r="B50" s="42"/>
       <c r="C50" s="75"/>
@@ -4719,8 +5011,17 @@
         <f>IF(AND(O50&gt;0,AB50="S"),O50*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE50" s="11" t="str">
+        <f>IF(AND(AD50="P",AB50&lt;&gt;"S"),N(R50)," ")</f>
+      </c>
+      <c r="AF50" s="11" t="str">
+        <f>IF(AND(AD50="P",AB50="S"),N(AC50)," ")</f>
+      </c>
+      <c r="AG50" s="11" t="str">
+        <f>IF(AD50="P",N(S50)," ")</f>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A51" s="101"/>
       <c r="B51" s="42"/>
       <c r="C51" s="75"/>
@@ -4788,8 +5089,17 @@
         <f>IF(AND(O51&gt;0,AB51="S"),O51*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE51" s="11" t="str">
+        <f>IF(AND(AD51="P",AB51&lt;&gt;"S"),N(R51)," ")</f>
+      </c>
+      <c r="AF51" s="11" t="str">
+        <f>IF(AND(AD51="P",AB51="S"),N(AC51)," ")</f>
+      </c>
+      <c r="AG51" s="11" t="str">
+        <f>IF(AD51="P",N(S51)," ")</f>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A52" s="101"/>
       <c r="B52" s="42"/>
       <c r="C52" s="75"/>
@@ -4857,8 +5167,17 @@
         <f>IF(AND(O52&gt;0,AB52="S"),O52*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE52" s="11" t="str">
+        <f>IF(AND(AD52="P",AB52&lt;&gt;"S"),N(R52)," ")</f>
+      </c>
+      <c r="AF52" s="11" t="str">
+        <f>IF(AND(AD52="P",AB52="S"),N(AC52)," ")</f>
+      </c>
+      <c r="AG52" s="11" t="str">
+        <f>IF(AD52="P",N(S52)," ")</f>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A53" s="101"/>
       <c r="B53" s="42"/>
       <c r="C53" s="75"/>
@@ -4926,8 +5245,17 @@
         <f>IF(AND(O53&gt;0,AB53="S"),O53*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE53" s="11" t="str">
+        <f>IF(AND(AD53="P",AB53&lt;&gt;"S"),N(R53)," ")</f>
+      </c>
+      <c r="AF53" s="11" t="str">
+        <f>IF(AND(AD53="P",AB53="S"),N(AC53)," ")</f>
+      </c>
+      <c r="AG53" s="11" t="str">
+        <f>IF(AD53="P",N(S53)," ")</f>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A54" s="101"/>
       <c r="B54" s="42"/>
       <c r="C54" s="75"/>
@@ -4995,8 +5323,17 @@
         <f>IF(AND(O54&gt;0,AB54="S"),O54*AC$4," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE54" s="11" t="str">
+        <f>IF(AND(AD54="P",AB54&lt;&gt;"S"),N(R54)," ")</f>
+      </c>
+      <c r="AF54" s="11" t="str">
+        <f>IF(AND(AD54="P",AB54="S"),N(AC54)," ")</f>
+      </c>
+      <c r="AG54" s="11" t="str">
+        <f>IF(AD54="P",N(S54)," ")</f>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A55" s="101"/>
       <c r="B55" s="117" t="s">
         <v>71</v>
@@ -5076,8 +5413,17 @@
         <f>SUM(AC38:AC54)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AE55" s="17">
+        <f>SUM(AE38:AE54)</f>
+      </c>
+      <c r="AF55" s="17">
+        <f>SUM(AF38:AF54)</f>
+      </c>
+      <c r="AG55" s="17">
+        <f>SUM(AG38:AG54)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:33" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A56" s="101"/>
       <c r="B56" s="12"/>
       <c r="C56" s="77"/>
@@ -5106,7 +5452,7 @@
       <c r="Z56" s="11"/>
       <c r="AA56" s="22"/>
     </row>
-    <row r="57" spans="1:29" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A57" s="101"/>
       <c r="B57" s="152" t="str">
         <f>B6</f>
@@ -5190,8 +5536,17 @@
         <f>AC11+AC19+AC27+AC35+AC55</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:29" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AE57" s="19">
+        <f>AE11+AE19+AE27+AE35+AE55</f>
+      </c>
+      <c r="AF57" s="19">
+        <f>AF11+AF19+AF27+AF35+AF55</f>
+      </c>
+      <c r="AG57" s="19">
+        <f>AG11+AG19+AG27+AG35+AG55</f>
+      </c>
+    </row>
+    <row r="58" spans="1:33" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A58" s="101"/>
       <c r="B58" s="14"/>
       <c r="C58" s="78"/>
@@ -5220,7 +5575,7 @@
       <c r="Z58" s="11"/>
       <c r="AA58" s="22"/>
     </row>
-    <row r="59" spans="1:29" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A59" s="101"/>
       <c r="B59" s="152" t="s">
         <v>62</v>
@@ -5254,7 +5609,7 @@
       <c r="Z59" s="11"/>
       <c r="AA59" s="22"/>
     </row>
-    <row r="60" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="101"/>
       <c r="B60" s="122" t="s">
         <v>10</v>
@@ -5288,7 +5643,7 @@
       <c r="Z60" s="11"/>
       <c r="AA60" s="22"/>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A61" s="101"/>
       <c r="B61" s="42"/>
       <c r="C61" s="75"/>
@@ -5335,7 +5690,7 @@
       <c r="Z61" s="11"/>
       <c r="AA61" s="22"/>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A62" s="101"/>
       <c r="B62" s="42"/>
       <c r="C62" s="75"/>
@@ -5382,7 +5737,7 @@
       <c r="Z62" s="11"/>
       <c r="AA62" s="22"/>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A63" s="101"/>
       <c r="B63" s="42"/>
       <c r="C63" s="75"/>
@@ -5429,7 +5784,7 @@
       <c r="Z63" s="11"/>
       <c r="AA63" s="22"/>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A64" s="101"/>
       <c r="B64" s="117" t="s">
         <v>12</v>
@@ -5509,8 +5864,17 @@
         <f>SUM(AC61:AC63)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE64" s="17">
+        <f>SUM(AE61:AE63)</f>
+      </c>
+      <c r="AF64" s="17">
+        <f>SUM(AF61:AF63)</f>
+      </c>
+      <c r="AG64" s="17">
+        <f>SUM(AG61:AG63)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="101"/>
       <c r="B65" s="37"/>
       <c r="C65" s="76"/>
@@ -5539,7 +5903,7 @@
       <c r="Z65" s="7"/>
       <c r="AA65" s="22"/>
     </row>
-    <row r="66" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="101"/>
       <c r="B66" s="122" t="s">
         <v>9</v>
@@ -5573,7 +5937,7 @@
       <c r="Z66" s="11"/>
       <c r="AA66" s="22"/>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A67" s="101"/>
       <c r="B67" s="42"/>
       <c r="C67" s="75"/>
@@ -5635,7 +5999,7 @@
       </c>
       <c r="AA67" s="22"/>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A68" s="101"/>
       <c r="B68" s="42"/>
       <c r="C68" s="75"/>
@@ -5697,7 +6061,7 @@
       </c>
       <c r="AA68" s="22"/>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A69" s="101"/>
       <c r="B69" s="42"/>
       <c r="C69" s="75"/>
@@ -5759,7 +6123,7 @@
       </c>
       <c r="AA69" s="22"/>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A70" s="101"/>
       <c r="B70" s="42"/>
       <c r="C70" s="75"/>
@@ -5821,7 +6185,7 @@
       </c>
       <c r="AA70" s="22"/>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A71" s="101"/>
       <c r="B71" s="42"/>
       <c r="C71" s="75"/>
@@ -5883,7 +6247,7 @@
       </c>
       <c r="AA71" s="22"/>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A72" s="101"/>
       <c r="B72" s="117" t="s">
         <v>13</v>
@@ -5963,8 +6327,17 @@
         <f>SUM(AC67:AC71)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE72" s="17">
+        <f>SUM(AE67:AE71)</f>
+      </c>
+      <c r="AF72" s="17">
+        <f>SUM(AF67:AF71)</f>
+      </c>
+      <c r="AG72" s="17">
+        <f>SUM(AG67:AG71)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="101"/>
       <c r="B73" s="37"/>
       <c r="C73" s="76"/>
@@ -5993,7 +6366,7 @@
       <c r="Z73" s="7"/>
       <c r="AA73" s="22"/>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A74" s="101"/>
       <c r="B74" s="122" t="s">
         <v>55</v>
@@ -6027,7 +6400,7 @@
       <c r="Z74" s="11"/>
       <c r="AA74" s="22"/>
     </row>
-    <row r="75" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="101"/>
       <c r="B75" s="42"/>
       <c r="C75" s="75"/>
@@ -6089,7 +6462,7 @@
       </c>
       <c r="AA75" s="22"/>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A76" s="101"/>
       <c r="B76" s="42"/>
       <c r="C76" s="75"/>
@@ -6151,7 +6524,7 @@
       </c>
       <c r="AA76" s="22"/>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A77" s="101"/>
       <c r="B77" s="42"/>
       <c r="C77" s="75"/>
@@ -6213,7 +6586,7 @@
       </c>
       <c r="AA77" s="22"/>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A78" s="101"/>
       <c r="B78" s="42"/>
       <c r="C78" s="75"/>
@@ -6275,7 +6648,7 @@
       </c>
       <c r="AA78" s="22"/>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A79" s="101"/>
       <c r="B79" s="42"/>
       <c r="C79" s="75"/>
@@ -6337,7 +6710,7 @@
       </c>
       <c r="AA79" s="22"/>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A80" s="101"/>
       <c r="B80" s="117" t="s">
         <v>14</v>
@@ -6417,8 +6790,17 @@
         <f>SUM(AC75:AC79)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE80" s="17">
+        <f>SUM(AE75:AE79)</f>
+      </c>
+      <c r="AF80" s="17">
+        <f>SUM(AF75:AF79)</f>
+      </c>
+      <c r="AG80" s="17">
+        <f>SUM(AG75:AG79)</f>
+      </c>
+    </row>
+    <row r="81" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="101"/>
       <c r="B81" s="37"/>
       <c r="C81" s="76"/>
@@ -6447,7 +6829,7 @@
       <c r="Z81" s="7"/>
       <c r="AA81" s="22"/>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A82" s="101"/>
       <c r="B82" s="122" t="s">
         <v>7</v>
@@ -6481,7 +6863,7 @@
       <c r="Z82" s="11"/>
       <c r="AA82" s="22"/>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A83" s="101"/>
       <c r="B83" s="42"/>
       <c r="C83" s="75"/>
@@ -6543,7 +6925,7 @@
       </c>
       <c r="AA83" s="22"/>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A84" s="101"/>
       <c r="B84" s="42"/>
       <c r="C84" s="75"/>
@@ -6605,7 +6987,7 @@
       </c>
       <c r="AA84" s="22"/>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A85" s="101"/>
       <c r="B85" s="42"/>
       <c r="C85" s="75"/>
@@ -6667,7 +7049,7 @@
       </c>
       <c r="AA85" s="22"/>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A86" s="101"/>
       <c r="B86" s="42"/>
       <c r="C86" s="75"/>
@@ -6729,7 +7111,7 @@
       </c>
       <c r="AA86" s="22"/>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A87" s="101"/>
       <c r="B87" s="42"/>
       <c r="C87" s="75"/>
@@ -6791,7 +7173,7 @@
       </c>
       <c r="AA87" s="22"/>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A88" s="101"/>
       <c r="B88" s="117" t="s">
         <v>15</v>
@@ -6871,8 +7253,17 @@
         <f>SUM(AC83:AC87)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE88" s="17">
+        <f>SUM(AE83:AE87)</f>
+      </c>
+      <c r="AF88" s="17">
+        <f>SUM(AF83:AF87)</f>
+      </c>
+      <c r="AG88" s="17">
+        <f>SUM(AG83:AG87)</f>
+      </c>
+    </row>
+    <row r="89" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="101"/>
       <c r="B89" s="37"/>
       <c r="C89" s="76"/>
@@ -6901,7 +7292,7 @@
       <c r="Z89" s="7"/>
       <c r="AA89" s="22"/>
     </row>
-    <row r="90" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="101"/>
       <c r="B90" s="120" t="str">
         <f>B37</f>
@@ -6939,7 +7330,7 @@
       <c r="Z90" s="11"/>
       <c r="AA90" s="22"/>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A91" s="101"/>
       <c r="B91" s="42"/>
       <c r="C91" s="75"/>
@@ -7004,8 +7395,17 @@
         <f>IF(AND(E91&gt;0,AB91="S"),E91*AC$4*(1-M91)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE91" s="11" t="str">
+        <f>IF(AND(AD91="P",AB91&lt;&gt;"S"),N(R91)," ")</f>
+      </c>
+      <c r="AF91" s="11" t="str">
+        <f>IF(AND(AD91="P",AB91="S"),N(AC91)," ")</f>
+      </c>
+      <c r="AG91" s="11" t="str">
+        <f>IF(AD91="P",N(S91)," ")</f>
+      </c>
+    </row>
+    <row r="92" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A92" s="101"/>
       <c r="B92" s="42"/>
       <c r="C92" s="75"/>
@@ -7070,8 +7470,17 @@
         <f>IF(AND(E92&gt;0,AB92="S"),E92*AC$4*(1-M92)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE92" s="11" t="str">
+        <f>IF(AND(AD92="P",AB92&lt;&gt;"S"),N(R92)," ")</f>
+      </c>
+      <c r="AF92" s="11" t="str">
+        <f>IF(AND(AD92="P",AB92="S"),N(AC92)," ")</f>
+      </c>
+      <c r="AG92" s="11" t="str">
+        <f>IF(AD92="P",N(S92)," ")</f>
+      </c>
+    </row>
+    <row r="93" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A93" s="101"/>
       <c r="B93" s="42"/>
       <c r="C93" s="75"/>
@@ -7136,8 +7545,17 @@
         <f>IF(AND(E93&gt;0,AB93="S"),E93*AC$4*(1-M93)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE93" s="11" t="str">
+        <f>IF(AND(AD93="P",AB93&lt;&gt;"S"),N(R93)," ")</f>
+      </c>
+      <c r="AF93" s="11" t="str">
+        <f>IF(AND(AD93="P",AB93="S"),N(AC93)," ")</f>
+      </c>
+      <c r="AG93" s="11" t="str">
+        <f>IF(AD93="P",N(S93)," ")</f>
+      </c>
+    </row>
+    <row r="94" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A94" s="101"/>
       <c r="B94" s="42"/>
       <c r="C94" s="75"/>
@@ -7202,8 +7620,17 @@
         <f>IF(AND(E94&gt;0,AB94="S"),E94*AC$4*(1-M94)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE94" s="11" t="str">
+        <f>IF(AND(AD94="P",AB94&lt;&gt;"S"),N(R94)," ")</f>
+      </c>
+      <c r="AF94" s="11" t="str">
+        <f>IF(AND(AD94="P",AB94="S"),N(AC94)," ")</f>
+      </c>
+      <c r="AG94" s="11" t="str">
+        <f>IF(AD94="P",N(S94)," ")</f>
+      </c>
+    </row>
+    <row r="95" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A95" s="101"/>
       <c r="B95" s="42"/>
       <c r="C95" s="75"/>
@@ -7268,8 +7695,17 @@
         <f>IF(AND(E95&gt;0,AB95="S"),E95*AC$4*(1-M95)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="96" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE95" s="11" t="str">
+        <f>IF(AND(AD95="P",AB95&lt;&gt;"S"),N(R95)," ")</f>
+      </c>
+      <c r="AF95" s="11" t="str">
+        <f>IF(AND(AD95="P",AB95="S"),N(AC95)," ")</f>
+      </c>
+      <c r="AG95" s="11" t="str">
+        <f>IF(AD95="P",N(S95)," ")</f>
+      </c>
+    </row>
+    <row r="96" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="101"/>
       <c r="B96" s="155" t="str">
         <f>B43</f>
@@ -7304,7 +7740,7 @@
       <c r="Z96" s="11"/>
       <c r="AA96" s="22"/>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A97" s="101"/>
       <c r="B97" s="42"/>
       <c r="C97" s="75"/>
@@ -7369,8 +7805,17 @@
         <f>IF(AND(E97&gt;0,AB97="S"),E97*AC$4*(1-M97)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE97" s="11" t="str">
+        <f>IF(AND(AD97="P",AB97&lt;&gt;"S"),N(R97)," ")</f>
+      </c>
+      <c r="AF97" s="11" t="str">
+        <f>IF(AND(AD97="P",AB97="S"),N(AC97)," ")</f>
+      </c>
+      <c r="AG97" s="11" t="str">
+        <f>IF(AD97="P",N(S97)," ")</f>
+      </c>
+    </row>
+    <row r="98" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A98" s="101"/>
       <c r="B98" s="42"/>
       <c r="C98" s="75"/>
@@ -7435,8 +7880,17 @@
         <f>IF(AND(E98&gt;0,AB98="S"),E98*AC$4*(1-M98)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE98" s="11" t="str">
+        <f>IF(AND(AD98="P",AB98&lt;&gt;"S"),N(R98)," ")</f>
+      </c>
+      <c r="AF98" s="11" t="str">
+        <f>IF(AND(AD98="P",AB98="S"),N(AC98)," ")</f>
+      </c>
+      <c r="AG98" s="11" t="str">
+        <f>IF(AD98="P",N(S98)," ")</f>
+      </c>
+    </row>
+    <row r="99" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A99" s="101"/>
       <c r="B99" s="42"/>
       <c r="C99" s="75"/>
@@ -7501,8 +7955,17 @@
         <f>IF(AND(E99&gt;0,AB99="S"),E99*AC$4*(1-M99)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE99" s="11" t="str">
+        <f>IF(AND(AD99="P",AB99&lt;&gt;"S"),N(R99)," ")</f>
+      </c>
+      <c r="AF99" s="11" t="str">
+        <f>IF(AND(AD99="P",AB99="S"),N(AC99)," ")</f>
+      </c>
+      <c r="AG99" s="11" t="str">
+        <f>IF(AD99="P",N(S99)," ")</f>
+      </c>
+    </row>
+    <row r="100" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A100" s="101"/>
       <c r="B100" s="42"/>
       <c r="C100" s="75"/>
@@ -7567,8 +8030,17 @@
         <f>IF(AND(E100&gt;0,AB100="S"),E100*AC$4*(1-M100)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE100" s="11" t="str">
+        <f>IF(AND(AD100="P",AB100&lt;&gt;"S"),N(R100)," ")</f>
+      </c>
+      <c r="AF100" s="11" t="str">
+        <f>IF(AND(AD100="P",AB100="S"),N(AC100)," ")</f>
+      </c>
+      <c r="AG100" s="11" t="str">
+        <f>IF(AD100="P",N(S100)," ")</f>
+      </c>
+    </row>
+    <row r="101" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A101" s="101"/>
       <c r="B101" s="42"/>
       <c r="C101" s="75"/>
@@ -7633,8 +8105,17 @@
         <f>IF(AND(E101&gt;0,AB101="S"),E101*AC$4*(1-M101)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-    </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AE101" s="11" t="str">
+        <f>IF(AND(AD101="P",AB101&lt;&gt;"S"),N(R101)," ")</f>
+      </c>
+      <c r="AF101" s="11" t="str">
+        <f>IF(AND(AD101="P",AB101="S"),N(AC101)," ")</f>
+      </c>
+      <c r="AG101" s="11" t="str">
+        <f>IF(AD101="P",N(S101)," ")</f>
+      </c>
+    </row>
+    <row r="102" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A102" s="101"/>
       <c r="B102" s="122" t="s">
         <v>54</v>
@@ -7665,7 +8146,7 @@
       <c r="Z102" s="11"/>
       <c r="AA102" s="22"/>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A103" s="101"/>
       <c r="B103" s="42"/>
       <c r="C103" s="75"/>
@@ -7729,7 +8210,7 @@
       </c>
       <c r="AA103" s="22"/>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A104" s="101"/>
       <c r="B104" s="42"/>
       <c r="C104" s="75"/>
@@ -7793,7 +8274,7 @@
       </c>
       <c r="AA104" s="22"/>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A105" s="101"/>
       <c r="B105" s="42"/>
       <c r="C105" s="75"/>
@@ -7857,7 +8338,7 @@
       </c>
       <c r="AA105" s="22"/>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A106" s="101"/>
       <c r="B106" s="42"/>
       <c r="C106" s="75"/>
@@ -7921,7 +8402,7 @@
       </c>
       <c r="AA106" s="22"/>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A107" s="101"/>
       <c r="B107" s="42"/>
       <c r="C107" s="75"/>
@@ -7985,7 +8466,7 @@
       </c>
       <c r="AA107" s="22"/>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A108" s="101"/>
       <c r="B108" s="117" t="s">
         <v>16</v>
@@ -8065,8 +8546,17 @@
         <f>SUM(AC91:AC107)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:29" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AE108" s="17">
+        <f>SUM(AE91:AE107)</f>
+      </c>
+      <c r="AF108" s="17">
+        <f>SUM(AF91:AF107)</f>
+      </c>
+      <c r="AG108" s="17">
+        <f>SUM(AG91:AG107)</f>
+      </c>
+    </row>
+    <row r="109" spans="1:33" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A109" s="101"/>
       <c r="B109" s="12"/>
       <c r="C109" s="77"/>
@@ -8095,7 +8585,7 @@
       <c r="Z109" s="11"/>
       <c r="AA109" s="22"/>
     </row>
-    <row r="110" spans="1:29" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A110" s="101"/>
       <c r="B110" s="152" t="str">
         <f>B59</f>
@@ -8179,8 +8669,17 @@
         <f>AC64+AC72+AC80+AC88+AC108</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:29" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AE110" s="19">
+        <f>AE64+AE72+AE80+AE88+AE108</f>
+      </c>
+      <c r="AF110" s="19">
+        <f>AF64+AF72+AF80+AF88+AF108</f>
+      </c>
+      <c r="AG110" s="19">
+        <f>AG64+AG72+AG80+AG88+AG108</f>
+      </c>
+    </row>
+    <row r="111" spans="1:33" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A111" s="102"/>
       <c r="B111" s="24"/>
       <c r="C111" s="79"/>

--- a/packages/GB Accounts Self Employed 2023-04-05 (Apr23) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Self Employed 2023-04-05 (Apr23) Excel 2007/Fixedassets.xlsx
@@ -1781,7 +1781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG111"/>
+  <dimension ref="A1:AI111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="5" customWidth="1"/>
@@ -1812,11 +1812,11 @@
     <col min="28" max="28" width="5.6640625" style="89" customWidth="1"/>
     <col min="29" max="29" width="10.6640625" style="2" customWidth="1"/>
     <col min="30" max="30" width="5.6640625" style="89" customWidth="1"/>
-    <col min="31" max="33" width="10.6640625" style="2" customWidth="1"/>
-    <col min="34" max="16384" width="9.1640625" style="5"/>
+    <col min="31" max="35" width="10.6640625" style="2" customWidth="1"/>
+    <col min="36" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="123"/>
       <c r="B1" s="134" t="s">
         <v>0</v>
@@ -1915,8 +1915,14 @@
       <c r="AG1" s="20">
         <f>AG57+AG110</f>
       </c>
-    </row>
-    <row r="2" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH1" s="20">
+        <f>AH57+AH110</f>
+      </c>
+      <c r="AI1" s="20">
+        <f>AI57+AI110</f>
+      </c>
+    </row>
+    <row r="2" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="124"/>
       <c r="B2" s="134"/>
       <c r="C2" s="135" t="s">
@@ -2008,8 +2014,18 @@
           <t>Single Asset Pool Written Down Tax Value</t>
         </is>
       </c>
-    </row>
-    <row r="3" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH2" s="132" t="inlineStr">
+        <is>
+          <t>Written Down Tax Value main pool</t>
+        </is>
+      </c>
+      <c r="AI2" s="132" t="inlineStr">
+        <is>
+          <t>Written Down Tax Value special rate pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="124"/>
       <c r="B3" s="134"/>
       <c r="C3" s="136"/>
@@ -2038,7 +2054,7 @@
       <c r="Z3" s="132"/>
       <c r="AA3" s="22"/>
     </row>
-    <row r="4" spans="1:33" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" s="16" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="124"/>
       <c r="B4" s="134"/>
       <c r="C4" s="136"/>
@@ -2096,7 +2112,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="16" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" s="16" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="100"/>
       <c r="B5" s="55"/>
       <c r="C5" s="74"/>
@@ -2125,7 +2141,7 @@
       <c r="Z5" s="57"/>
       <c r="AA5" s="23"/>
     </row>
-    <row r="6" spans="1:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="101"/>
       <c r="B6" s="152" t="s">
         <v>61</v>
@@ -2159,7 +2175,7 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="22"/>
     </row>
-    <row r="7" spans="1:33" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:35" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="101"/>
       <c r="B7" s="122" t="s">
         <v>10</v>
@@ -2193,7 +2209,7 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="22"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A8" s="101"/>
       <c r="B8" s="42"/>
       <c r="C8" s="75"/>
@@ -2243,7 +2259,7 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="22"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A9" s="101"/>
       <c r="B9" s="42"/>
       <c r="C9" s="75"/>
@@ -2293,7 +2309,7 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="22"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A10" s="101"/>
       <c r="B10" s="42"/>
       <c r="C10" s="75"/>
@@ -2343,7 +2359,7 @@
       <c r="Z10" s="11"/>
       <c r="AA10" s="22"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A11" s="101"/>
       <c r="B11" s="117" t="s">
         <v>67</v>
@@ -2432,8 +2448,14 @@
       <c r="AG11" s="17">
         <f>SUM(AG8:AG10)</f>
       </c>
-    </row>
-    <row r="12" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH11" s="17">
+        <f>SUM(AH8:AH10)</f>
+      </c>
+      <c r="AI11" s="17">
+        <f>SUM(AI8:AI10)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="101"/>
       <c r="B12" s="37"/>
       <c r="C12" s="76"/>
@@ -2462,7 +2484,7 @@
       <c r="Z12" s="7"/>
       <c r="AA12" s="22"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A13" s="101"/>
       <c r="B13" s="122" t="s">
         <v>9</v>
@@ -2496,7 +2518,7 @@
       <c r="Z13" s="11"/>
       <c r="AA13" s="22"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A14" s="101"/>
       <c r="B14" s="42"/>
       <c r="C14" s="75"/>
@@ -2571,8 +2593,14 @@
       <c r="AG14" s="11" t="str">
         <f>IF(AD14="P",N(S14)," ")</f>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH14" s="11" t="str">
+        <f>IF(AND(AD14&lt;&gt;"P",AB14&lt;&gt;"S"),N(S14)," ")</f>
+      </c>
+      <c r="AI14" s="11" t="str">
+        <f>IF(AND(AD14&lt;&gt;"P",AB14="S"),N(S14)," ")</f>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A15" s="101"/>
       <c r="B15" s="42"/>
       <c r="C15" s="75"/>
@@ -2647,8 +2675,14 @@
       <c r="AG15" s="11" t="str">
         <f>IF(AD15="P",N(S15)," ")</f>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH15" s="11" t="str">
+        <f>IF(AND(AD15&lt;&gt;"P",AB15&lt;&gt;"S"),N(S15)," ")</f>
+      </c>
+      <c r="AI15" s="11" t="str">
+        <f>IF(AND(AD15&lt;&gt;"P",AB15="S"),N(S15)," ")</f>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A16" s="101"/>
       <c r="B16" s="42"/>
       <c r="C16" s="75"/>
@@ -2723,8 +2757,14 @@
       <c r="AG16" s="11" t="str">
         <f>IF(AD16="P",N(S16)," ")</f>
       </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH16" s="11" t="str">
+        <f>IF(AND(AD16&lt;&gt;"P",AB16&lt;&gt;"S"),N(S16)," ")</f>
+      </c>
+      <c r="AI16" s="11" t="str">
+        <f>IF(AND(AD16&lt;&gt;"P",AB16="S"),N(S16)," ")</f>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A17" s="101"/>
       <c r="B17" s="42"/>
       <c r="C17" s="75"/>
@@ -2799,8 +2839,14 @@
       <c r="AG17" s="11" t="str">
         <f>IF(AD17="P",N(S17)," ")</f>
       </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH17" s="11" t="str">
+        <f>IF(AND(AD17&lt;&gt;"P",AB17&lt;&gt;"S"),N(S17)," ")</f>
+      </c>
+      <c r="AI17" s="11" t="str">
+        <f>IF(AND(AD17&lt;&gt;"P",AB17="S"),N(S17)," ")</f>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A18" s="101"/>
       <c r="B18" s="42"/>
       <c r="C18" s="75"/>
@@ -2875,8 +2921,14 @@
       <c r="AG18" s="11" t="str">
         <f>IF(AD18="P",N(S18)," ")</f>
       </c>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH18" s="11" t="str">
+        <f>IF(AND(AD18&lt;&gt;"P",AB18&lt;&gt;"S"),N(S18)," ")</f>
+      </c>
+      <c r="AI18" s="11" t="str">
+        <f>IF(AND(AD18&lt;&gt;"P",AB18="S"),N(S18)," ")</f>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A19" s="101"/>
       <c r="B19" s="117" t="s">
         <v>68</v>
@@ -2965,8 +3017,14 @@
       <c r="AG19" s="17">
         <f>SUM(AG14:AG18)</f>
       </c>
-    </row>
-    <row r="20" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH19" s="17">
+        <f>SUM(AH14:AH18)</f>
+      </c>
+      <c r="AI19" s="17">
+        <f>SUM(AI14:AI18)</f>
+      </c>
+    </row>
+    <row r="20" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="101"/>
       <c r="B20" s="37"/>
       <c r="C20" s="76"/>
@@ -2995,7 +3053,7 @@
       <c r="Z20" s="7"/>
       <c r="AA20" s="22"/>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A21" s="101"/>
       <c r="B21" s="122" t="s">
         <v>55</v>
@@ -3029,7 +3087,7 @@
       <c r="Z21" s="11"/>
       <c r="AA21" s="22"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A22" s="101"/>
       <c r="B22" s="42"/>
       <c r="C22" s="75"/>
@@ -3104,8 +3162,14 @@
       <c r="AG22" s="11" t="str">
         <f>IF(AD22="P",N(S22)," ")</f>
       </c>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH22" s="11" t="str">
+        <f>IF(AND(AD22&lt;&gt;"P",AB22&lt;&gt;"S"),N(S22)," ")</f>
+      </c>
+      <c r="AI22" s="11" t="str">
+        <f>IF(AND(AD22&lt;&gt;"P",AB22="S"),N(S22)," ")</f>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A23" s="101"/>
       <c r="B23" s="42"/>
       <c r="C23" s="75"/>
@@ -3180,8 +3244,14 @@
       <c r="AG23" s="11" t="str">
         <f>IF(AD23="P",N(S23)," ")</f>
       </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH23" s="11" t="str">
+        <f>IF(AND(AD23&lt;&gt;"P",AB23&lt;&gt;"S"),N(S23)," ")</f>
+      </c>
+      <c r="AI23" s="11" t="str">
+        <f>IF(AND(AD23&lt;&gt;"P",AB23="S"),N(S23)," ")</f>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A24" s="101"/>
       <c r="B24" s="42"/>
       <c r="C24" s="75"/>
@@ -3256,8 +3326,14 @@
       <c r="AG24" s="11" t="str">
         <f>IF(AD24="P",N(S24)," ")</f>
       </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH24" s="11" t="str">
+        <f>IF(AND(AD24&lt;&gt;"P",AB24&lt;&gt;"S"),N(S24)," ")</f>
+      </c>
+      <c r="AI24" s="11" t="str">
+        <f>IF(AND(AD24&lt;&gt;"P",AB24="S"),N(S24)," ")</f>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A25" s="101"/>
       <c r="B25" s="42"/>
       <c r="C25" s="75"/>
@@ -3332,8 +3408,14 @@
       <c r="AG25" s="11" t="str">
         <f>IF(AD25="P",N(S25)," ")</f>
       </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH25" s="11" t="str">
+        <f>IF(AND(AD25&lt;&gt;"P",AB25&lt;&gt;"S"),N(S25)," ")</f>
+      </c>
+      <c r="AI25" s="11" t="str">
+        <f>IF(AND(AD25&lt;&gt;"P",AB25="S"),N(S25)," ")</f>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A26" s="101"/>
       <c r="B26" s="42"/>
       <c r="C26" s="75"/>
@@ -3408,8 +3490,14 @@
       <c r="AG26" s="11" t="str">
         <f>IF(AD26="P",N(S26)," ")</f>
       </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH26" s="11" t="str">
+        <f>IF(AND(AD26&lt;&gt;"P",AB26&lt;&gt;"S"),N(S26)," ")</f>
+      </c>
+      <c r="AI26" s="11" t="str">
+        <f>IF(AND(AD26&lt;&gt;"P",AB26="S"),N(S26)," ")</f>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A27" s="101"/>
       <c r="B27" s="117" t="s">
         <v>69</v>
@@ -3498,8 +3586,14 @@
       <c r="AG27" s="17">
         <f>SUM(AG22:AG26)</f>
       </c>
-    </row>
-    <row r="28" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH27" s="17">
+        <f>SUM(AH22:AH26)</f>
+      </c>
+      <c r="AI27" s="17">
+        <f>SUM(AI22:AI26)</f>
+      </c>
+    </row>
+    <row r="28" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="101"/>
       <c r="B28" s="37"/>
       <c r="C28" s="76"/>
@@ -3528,7 +3622,7 @@
       <c r="Z28" s="7"/>
       <c r="AA28" s="22"/>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A29" s="101"/>
       <c r="B29" s="122" t="s">
         <v>7</v>
@@ -3562,7 +3656,7 @@
       <c r="Z29" s="11"/>
       <c r="AA29" s="22"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A30" s="101"/>
       <c r="B30" s="42"/>
       <c r="C30" s="75"/>
@@ -3637,8 +3731,14 @@
       <c r="AG30" s="11" t="str">
         <f>IF(AD30="P",N(S30)," ")</f>
       </c>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH30" s="11" t="str">
+        <f>IF(AND(AD30&lt;&gt;"P",AB30&lt;&gt;"S"),N(S30)," ")</f>
+      </c>
+      <c r="AI30" s="11" t="str">
+        <f>IF(AND(AD30&lt;&gt;"P",AB30="S"),N(S30)," ")</f>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A31" s="101"/>
       <c r="B31" s="42"/>
       <c r="C31" s="75"/>
@@ -3713,8 +3813,14 @@
       <c r="AG31" s="11" t="str">
         <f>IF(AD31="P",N(S31)," ")</f>
       </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH31" s="11" t="str">
+        <f>IF(AND(AD31&lt;&gt;"P",AB31&lt;&gt;"S"),N(S31)," ")</f>
+      </c>
+      <c r="AI31" s="11" t="str">
+        <f>IF(AND(AD31&lt;&gt;"P",AB31="S"),N(S31)," ")</f>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A32" s="101"/>
       <c r="B32" s="42"/>
       <c r="C32" s="75"/>
@@ -3789,8 +3895,14 @@
       <c r="AG32" s="11" t="str">
         <f>IF(AD32="P",N(S32)," ")</f>
       </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH32" s="11" t="str">
+        <f>IF(AND(AD32&lt;&gt;"P",AB32&lt;&gt;"S"),N(S32)," ")</f>
+      </c>
+      <c r="AI32" s="11" t="str">
+        <f>IF(AND(AD32&lt;&gt;"P",AB32="S"),N(S32)," ")</f>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A33" s="101"/>
       <c r="B33" s="42"/>
       <c r="C33" s="75"/>
@@ -3865,8 +3977,14 @@
       <c r="AG33" s="11" t="str">
         <f>IF(AD33="P",N(S33)," ")</f>
       </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH33" s="11" t="str">
+        <f>IF(AND(AD33&lt;&gt;"P",AB33&lt;&gt;"S"),N(S33)," ")</f>
+      </c>
+      <c r="AI33" s="11" t="str">
+        <f>IF(AND(AD33&lt;&gt;"P",AB33="S"),N(S33)," ")</f>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A34" s="101"/>
       <c r="B34" s="42"/>
       <c r="C34" s="75"/>
@@ -3941,8 +4059,14 @@
       <c r="AG34" s="11" t="str">
         <f>IF(AD34="P",N(S34)," ")</f>
       </c>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH34" s="11" t="str">
+        <f>IF(AND(AD34&lt;&gt;"P",AB34&lt;&gt;"S"),N(S34)," ")</f>
+      </c>
+      <c r="AI34" s="11" t="str">
+        <f>IF(AND(AD34&lt;&gt;"P",AB34="S"),N(S34)," ")</f>
+      </c>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A35" s="101"/>
       <c r="B35" s="117" t="s">
         <v>70</v>
@@ -4031,8 +4155,14 @@
       <c r="AG35" s="17">
         <f>SUM(AG30:AG34)</f>
       </c>
-    </row>
-    <row r="36" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH35" s="17">
+        <f>SUM(AH30:AH34)</f>
+      </c>
+      <c r="AI35" s="17">
+        <f>SUM(AI30:AI34)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="101"/>
       <c r="B36" s="37"/>
       <c r="C36" s="76"/>
@@ -4061,7 +4191,7 @@
       <c r="Z36" s="7"/>
       <c r="AA36" s="22"/>
     </row>
-    <row r="37" spans="1:33" ht="13" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:35" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="101"/>
       <c r="B37" s="120" t="s">
         <v>63</v>
@@ -4098,7 +4228,7 @@
       <c r="Z37" s="7"/>
       <c r="AA37" s="22"/>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A38" s="101"/>
       <c r="B38" s="42"/>
       <c r="C38" s="75"/>
@@ -4175,8 +4305,14 @@
       <c r="AG38" s="11" t="str">
         <f>IF(AD38="P",N(S38)," ")</f>
       </c>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH38" s="11" t="str">
+        <f>IF(AND(AD38&lt;&gt;"P",AB38&lt;&gt;"S"),N(S38)," ")</f>
+      </c>
+      <c r="AI38" s="11" t="str">
+        <f>IF(AND(AD38&lt;&gt;"P",AB38="S"),N(S38)," ")</f>
+      </c>
+    </row>
+    <row r="39" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A39" s="101"/>
       <c r="B39" s="42"/>
       <c r="C39" s="75"/>
@@ -4253,8 +4389,14 @@
       <c r="AG39" s="11" t="str">
         <f>IF(AD39="P",N(S39)," ")</f>
       </c>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH39" s="11" t="str">
+        <f>IF(AND(AD39&lt;&gt;"P",AB39&lt;&gt;"S"),N(S39)," ")</f>
+      </c>
+      <c r="AI39" s="11" t="str">
+        <f>IF(AND(AD39&lt;&gt;"P",AB39="S"),N(S39)," ")</f>
+      </c>
+    </row>
+    <row r="40" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A40" s="101"/>
       <c r="B40" s="42"/>
       <c r="C40" s="75"/>
@@ -4331,8 +4473,14 @@
       <c r="AG40" s="11" t="str">
         <f>IF(AD40="P",N(S40)," ")</f>
       </c>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH40" s="11" t="str">
+        <f>IF(AND(AD40&lt;&gt;"P",AB40&lt;&gt;"S"),N(S40)," ")</f>
+      </c>
+      <c r="AI40" s="11" t="str">
+        <f>IF(AND(AD40&lt;&gt;"P",AB40="S"),N(S40)," ")</f>
+      </c>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A41" s="101"/>
       <c r="B41" s="42"/>
       <c r="C41" s="75"/>
@@ -4409,8 +4557,14 @@
       <c r="AG41" s="11" t="str">
         <f>IF(AD41="P",N(S41)," ")</f>
       </c>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH41" s="11" t="str">
+        <f>IF(AND(AD41&lt;&gt;"P",AB41&lt;&gt;"S"),N(S41)," ")</f>
+      </c>
+      <c r="AI41" s="11" t="str">
+        <f>IF(AND(AD41&lt;&gt;"P",AB41="S"),N(S41)," ")</f>
+      </c>
+    </row>
+    <row r="42" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A42" s="101"/>
       <c r="B42" s="42"/>
       <c r="C42" s="75"/>
@@ -4487,8 +4641,14 @@
       <c r="AG42" s="11" t="str">
         <f>IF(AD42="P",N(S42)," ")</f>
       </c>
-    </row>
-    <row r="43" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH42" s="11" t="str">
+        <f>IF(AND(AD42&lt;&gt;"P",AB42&lt;&gt;"S"),N(S42)," ")</f>
+      </c>
+      <c r="AI42" s="11" t="str">
+        <f>IF(AND(AD42&lt;&gt;"P",AB42="S"),N(S42)," ")</f>
+      </c>
+    </row>
+    <row r="43" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="101"/>
       <c r="B43" s="120" t="s">
         <v>64</v>
@@ -4522,7 +4682,7 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="22"/>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A44" s="101"/>
       <c r="B44" s="42"/>
       <c r="C44" s="75"/>
@@ -4599,8 +4759,14 @@
       <c r="AG44" s="11" t="str">
         <f>IF(AD44="P",N(S44)," ")</f>
       </c>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH44" s="11" t="str">
+        <f>IF(AND(AD44&lt;&gt;"P",AB44&lt;&gt;"S"),N(S44)," ")</f>
+      </c>
+      <c r="AI44" s="11" t="str">
+        <f>IF(AND(AD44&lt;&gt;"P",AB44="S"),N(S44)," ")</f>
+      </c>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A45" s="101"/>
       <c r="B45" s="42"/>
       <c r="C45" s="75"/>
@@ -4677,8 +4843,14 @@
       <c r="AG45" s="11" t="str">
         <f>IF(AD45="P",N(S45)," ")</f>
       </c>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH45" s="11" t="str">
+        <f>IF(AND(AD45&lt;&gt;"P",AB45&lt;&gt;"S"),N(S45)," ")</f>
+      </c>
+      <c r="AI45" s="11" t="str">
+        <f>IF(AND(AD45&lt;&gt;"P",AB45="S"),N(S45)," ")</f>
+      </c>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A46" s="101"/>
       <c r="B46" s="42"/>
       <c r="C46" s="75"/>
@@ -4755,8 +4927,14 @@
       <c r="AG46" s="11" t="str">
         <f>IF(AD46="P",N(S46)," ")</f>
       </c>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH46" s="11" t="str">
+        <f>IF(AND(AD46&lt;&gt;"P",AB46&lt;&gt;"S"),N(S46)," ")</f>
+      </c>
+      <c r="AI46" s="11" t="str">
+        <f>IF(AND(AD46&lt;&gt;"P",AB46="S"),N(S46)," ")</f>
+      </c>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A47" s="101"/>
       <c r="B47" s="42"/>
       <c r="C47" s="75"/>
@@ -4833,8 +5011,14 @@
       <c r="AG47" s="11" t="str">
         <f>IF(AD47="P",N(S47)," ")</f>
       </c>
-    </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH47" s="11" t="str">
+        <f>IF(AND(AD47&lt;&gt;"P",AB47&lt;&gt;"S"),N(S47)," ")</f>
+      </c>
+      <c r="AI47" s="11" t="str">
+        <f>IF(AND(AD47&lt;&gt;"P",AB47="S"),N(S47)," ")</f>
+      </c>
+    </row>
+    <row r="48" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A48" s="101"/>
       <c r="B48" s="42"/>
       <c r="C48" s="75"/>
@@ -4911,8 +5095,14 @@
       <c r="AG48" s="11" t="str">
         <f>IF(AD48="P",N(S48)," ")</f>
       </c>
-    </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH48" s="11" t="str">
+        <f>IF(AND(AD48&lt;&gt;"P",AB48&lt;&gt;"S"),N(S48)," ")</f>
+      </c>
+      <c r="AI48" s="11" t="str">
+        <f>IF(AND(AD48&lt;&gt;"P",AB48="S"),N(S48)," ")</f>
+      </c>
+    </row>
+    <row r="49" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A49" s="101"/>
       <c r="B49" s="122" t="s">
         <v>54</v>
@@ -4943,7 +5133,7 @@
       <c r="Z49" s="11"/>
       <c r="AA49" s="22"/>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A50" s="101"/>
       <c r="B50" s="42"/>
       <c r="C50" s="75"/>
@@ -5020,8 +5210,14 @@
       <c r="AG50" s="11" t="str">
         <f>IF(AD50="P",N(S50)," ")</f>
       </c>
-    </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH50" s="11" t="str">
+        <f>IF(AND(AD50&lt;&gt;"P",AB50&lt;&gt;"S"),N(S50)," ")</f>
+      </c>
+      <c r="AI50" s="11" t="str">
+        <f>IF(AND(AD50&lt;&gt;"P",AB50="S"),N(S50)," ")</f>
+      </c>
+    </row>
+    <row r="51" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A51" s="101"/>
       <c r="B51" s="42"/>
       <c r="C51" s="75"/>
@@ -5098,8 +5294,14 @@
       <c r="AG51" s="11" t="str">
         <f>IF(AD51="P",N(S51)," ")</f>
       </c>
-    </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH51" s="11" t="str">
+        <f>IF(AND(AD51&lt;&gt;"P",AB51&lt;&gt;"S"),N(S51)," ")</f>
+      </c>
+      <c r="AI51" s="11" t="str">
+        <f>IF(AND(AD51&lt;&gt;"P",AB51="S"),N(S51)," ")</f>
+      </c>
+    </row>
+    <row r="52" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A52" s="101"/>
       <c r="B52" s="42"/>
       <c r="C52" s="75"/>
@@ -5176,8 +5378,14 @@
       <c r="AG52" s="11" t="str">
         <f>IF(AD52="P",N(S52)," ")</f>
       </c>
-    </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH52" s="11" t="str">
+        <f>IF(AND(AD52&lt;&gt;"P",AB52&lt;&gt;"S"),N(S52)," ")</f>
+      </c>
+      <c r="AI52" s="11" t="str">
+        <f>IF(AND(AD52&lt;&gt;"P",AB52="S"),N(S52)," ")</f>
+      </c>
+    </row>
+    <row r="53" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A53" s="101"/>
       <c r="B53" s="42"/>
       <c r="C53" s="75"/>
@@ -5254,8 +5462,14 @@
       <c r="AG53" s="11" t="str">
         <f>IF(AD53="P",N(S53)," ")</f>
       </c>
-    </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH53" s="11" t="str">
+        <f>IF(AND(AD53&lt;&gt;"P",AB53&lt;&gt;"S"),N(S53)," ")</f>
+      </c>
+      <c r="AI53" s="11" t="str">
+        <f>IF(AND(AD53&lt;&gt;"P",AB53="S"),N(S53)," ")</f>
+      </c>
+    </row>
+    <row r="54" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A54" s="101"/>
       <c r="B54" s="42"/>
       <c r="C54" s="75"/>
@@ -5332,8 +5546,14 @@
       <c r="AG54" s="11" t="str">
         <f>IF(AD54="P",N(S54)," ")</f>
       </c>
-    </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH54" s="11" t="str">
+        <f>IF(AND(AD54&lt;&gt;"P",AB54&lt;&gt;"S"),N(S54)," ")</f>
+      </c>
+      <c r="AI54" s="11" t="str">
+        <f>IF(AND(AD54&lt;&gt;"P",AB54="S"),N(S54)," ")</f>
+      </c>
+    </row>
+    <row r="55" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A55" s="101"/>
       <c r="B55" s="117" t="s">
         <v>71</v>
@@ -5422,8 +5642,14 @@
       <c r="AG55" s="17">
         <f>SUM(AG38:AG54)</f>
       </c>
-    </row>
-    <row r="56" spans="1:33" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AH55" s="17">
+        <f>SUM(AH38:AH54)</f>
+      </c>
+      <c r="AI55" s="17">
+        <f>SUM(AI38:AI54)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:35" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A56" s="101"/>
       <c r="B56" s="12"/>
       <c r="C56" s="77"/>
@@ -5452,7 +5678,7 @@
       <c r="Z56" s="11"/>
       <c r="AA56" s="22"/>
     </row>
-    <row r="57" spans="1:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:35" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A57" s="101"/>
       <c r="B57" s="152" t="str">
         <f>B6</f>
@@ -5545,8 +5771,14 @@
       <c r="AG57" s="19">
         <f>AG11+AG19+AG27+AG35+AG55</f>
       </c>
-    </row>
-    <row r="58" spans="1:33" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AH57" s="19">
+        <f>AH11+AH19+AH27+AH35+AH55</f>
+      </c>
+      <c r="AI57" s="19">
+        <f>AI11+AI19+AI27+AI35+AI55</f>
+      </c>
+    </row>
+    <row r="58" spans="1:35" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A58" s="101"/>
       <c r="B58" s="14"/>
       <c r="C58" s="78"/>
@@ -5575,7 +5807,7 @@
       <c r="Z58" s="11"/>
       <c r="AA58" s="22"/>
     </row>
-    <row r="59" spans="1:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:35" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A59" s="101"/>
       <c r="B59" s="152" t="s">
         <v>62</v>
@@ -5609,7 +5841,7 @@
       <c r="Z59" s="11"/>
       <c r="AA59" s="22"/>
     </row>
-    <row r="60" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="101"/>
       <c r="B60" s="122" t="s">
         <v>10</v>
@@ -5643,7 +5875,7 @@
       <c r="Z60" s="11"/>
       <c r="AA60" s="22"/>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A61" s="101"/>
       <c r="B61" s="42"/>
       <c r="C61" s="75"/>
@@ -5690,7 +5922,7 @@
       <c r="Z61" s="11"/>
       <c r="AA61" s="22"/>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A62" s="101"/>
       <c r="B62" s="42"/>
       <c r="C62" s="75"/>
@@ -5737,7 +5969,7 @@
       <c r="Z62" s="11"/>
       <c r="AA62" s="22"/>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A63" s="101"/>
       <c r="B63" s="42"/>
       <c r="C63" s="75"/>
@@ -5784,7 +6016,7 @@
       <c r="Z63" s="11"/>
       <c r="AA63" s="22"/>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A64" s="101"/>
       <c r="B64" s="117" t="s">
         <v>12</v>
@@ -5873,8 +6105,14 @@
       <c r="AG64" s="17">
         <f>SUM(AG61:AG63)</f>
       </c>
-    </row>
-    <row r="65" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH64" s="17">
+        <f>SUM(AH61:AH63)</f>
+      </c>
+      <c r="AI64" s="17">
+        <f>SUM(AI61:AI63)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="101"/>
       <c r="B65" s="37"/>
       <c r="C65" s="76"/>
@@ -5903,7 +6141,7 @@
       <c r="Z65" s="7"/>
       <c r="AA65" s="22"/>
     </row>
-    <row r="66" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="101"/>
       <c r="B66" s="122" t="s">
         <v>9</v>
@@ -5937,7 +6175,7 @@
       <c r="Z66" s="11"/>
       <c r="AA66" s="22"/>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A67" s="101"/>
       <c r="B67" s="42"/>
       <c r="C67" s="75"/>
@@ -5999,7 +6237,7 @@
       </c>
       <c r="AA67" s="22"/>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A68" s="101"/>
       <c r="B68" s="42"/>
       <c r="C68" s="75"/>
@@ -6061,7 +6299,7 @@
       </c>
       <c r="AA68" s="22"/>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A69" s="101"/>
       <c r="B69" s="42"/>
       <c r="C69" s="75"/>
@@ -6123,7 +6361,7 @@
       </c>
       <c r="AA69" s="22"/>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A70" s="101"/>
       <c r="B70" s="42"/>
       <c r="C70" s="75"/>
@@ -6185,7 +6423,7 @@
       </c>
       <c r="AA70" s="22"/>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A71" s="101"/>
       <c r="B71" s="42"/>
       <c r="C71" s="75"/>
@@ -6247,7 +6485,7 @@
       </c>
       <c r="AA71" s="22"/>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A72" s="101"/>
       <c r="B72" s="117" t="s">
         <v>13</v>
@@ -6336,8 +6574,14 @@
       <c r="AG72" s="17">
         <f>SUM(AG67:AG71)</f>
       </c>
-    </row>
-    <row r="73" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH72" s="17">
+        <f>SUM(AH67:AH71)</f>
+      </c>
+      <c r="AI72" s="17">
+        <f>SUM(AI67:AI71)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="101"/>
       <c r="B73" s="37"/>
       <c r="C73" s="76"/>
@@ -6366,7 +6610,7 @@
       <c r="Z73" s="7"/>
       <c r="AA73" s="22"/>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A74" s="101"/>
       <c r="B74" s="122" t="s">
         <v>55</v>
@@ -6400,7 +6644,7 @@
       <c r="Z74" s="11"/>
       <c r="AA74" s="22"/>
     </row>
-    <row r="75" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="101"/>
       <c r="B75" s="42"/>
       <c r="C75" s="75"/>
@@ -6462,7 +6706,7 @@
       </c>
       <c r="AA75" s="22"/>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A76" s="101"/>
       <c r="B76" s="42"/>
       <c r="C76" s="75"/>
@@ -6524,7 +6768,7 @@
       </c>
       <c r="AA76" s="22"/>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A77" s="101"/>
       <c r="B77" s="42"/>
       <c r="C77" s="75"/>
@@ -6586,7 +6830,7 @@
       </c>
       <c r="AA77" s="22"/>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A78" s="101"/>
       <c r="B78" s="42"/>
       <c r="C78" s="75"/>
@@ -6648,7 +6892,7 @@
       </c>
       <c r="AA78" s="22"/>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A79" s="101"/>
       <c r="B79" s="42"/>
       <c r="C79" s="75"/>
@@ -6710,7 +6954,7 @@
       </c>
       <c r="AA79" s="22"/>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A80" s="101"/>
       <c r="B80" s="117" t="s">
         <v>14</v>
@@ -6799,8 +7043,14 @@
       <c r="AG80" s="17">
         <f>SUM(AG75:AG79)</f>
       </c>
-    </row>
-    <row r="81" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH80" s="17">
+        <f>SUM(AH75:AH79)</f>
+      </c>
+      <c r="AI80" s="17">
+        <f>SUM(AI75:AI79)</f>
+      </c>
+    </row>
+    <row r="81" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="101"/>
       <c r="B81" s="37"/>
       <c r="C81" s="76"/>
@@ -6829,7 +7079,7 @@
       <c r="Z81" s="7"/>
       <c r="AA81" s="22"/>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A82" s="101"/>
       <c r="B82" s="122" t="s">
         <v>7</v>
@@ -6863,7 +7113,7 @@
       <c r="Z82" s="11"/>
       <c r="AA82" s="22"/>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A83" s="101"/>
       <c r="B83" s="42"/>
       <c r="C83" s="75"/>
@@ -6925,7 +7175,7 @@
       </c>
       <c r="AA83" s="22"/>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A84" s="101"/>
       <c r="B84" s="42"/>
       <c r="C84" s="75"/>
@@ -6987,7 +7237,7 @@
       </c>
       <c r="AA84" s="22"/>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A85" s="101"/>
       <c r="B85" s="42"/>
       <c r="C85" s="75"/>
@@ -7049,7 +7299,7 @@
       </c>
       <c r="AA85" s="22"/>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A86" s="101"/>
       <c r="B86" s="42"/>
       <c r="C86" s="75"/>
@@ -7111,7 +7361,7 @@
       </c>
       <c r="AA86" s="22"/>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A87" s="101"/>
       <c r="B87" s="42"/>
       <c r="C87" s="75"/>
@@ -7173,7 +7423,7 @@
       </c>
       <c r="AA87" s="22"/>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A88" s="101"/>
       <c r="B88" s="117" t="s">
         <v>15</v>
@@ -7262,8 +7512,14 @@
       <c r="AG88" s="17">
         <f>SUM(AG83:AG87)</f>
       </c>
-    </row>
-    <row r="89" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH88" s="17">
+        <f>SUM(AH83:AH87)</f>
+      </c>
+      <c r="AI88" s="17">
+        <f>SUM(AI83:AI87)</f>
+      </c>
+    </row>
+    <row r="89" spans="1:35" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="101"/>
       <c r="B89" s="37"/>
       <c r="C89" s="76"/>
@@ -7292,7 +7548,7 @@
       <c r="Z89" s="7"/>
       <c r="AA89" s="22"/>
     </row>
-    <row r="90" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="101"/>
       <c r="B90" s="120" t="str">
         <f>B37</f>
@@ -7330,7 +7586,7 @@
       <c r="Z90" s="11"/>
       <c r="AA90" s="22"/>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A91" s="101"/>
       <c r="B91" s="42"/>
       <c r="C91" s="75"/>
@@ -7404,8 +7660,14 @@
       <c r="AG91" s="11" t="str">
         <f>IF(AD91="P",N(S91)," ")</f>
       </c>
-    </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH91" s="11" t="str">
+        <f>IF(AND(AD91&lt;&gt;"P",AB91&lt;&gt;"S"),N(S91)," ")</f>
+      </c>
+      <c r="AI91" s="11" t="str">
+        <f>IF(AND(AD91&lt;&gt;"P",AB91="S"),N(S91)," ")</f>
+      </c>
+    </row>
+    <row r="92" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A92" s="101"/>
       <c r="B92" s="42"/>
       <c r="C92" s="75"/>
@@ -7479,8 +7741,14 @@
       <c r="AG92" s="11" t="str">
         <f>IF(AD92="P",N(S92)," ")</f>
       </c>
-    </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH92" s="11" t="str">
+        <f>IF(AND(AD92&lt;&gt;"P",AB92&lt;&gt;"S"),N(S92)," ")</f>
+      </c>
+      <c r="AI92" s="11" t="str">
+        <f>IF(AND(AD92&lt;&gt;"P",AB92="S"),N(S92)," ")</f>
+      </c>
+    </row>
+    <row r="93" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A93" s="101"/>
       <c r="B93" s="42"/>
       <c r="C93" s="75"/>
@@ -7554,8 +7822,14 @@
       <c r="AG93" s="11" t="str">
         <f>IF(AD93="P",N(S93)," ")</f>
       </c>
-    </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH93" s="11" t="str">
+        <f>IF(AND(AD93&lt;&gt;"P",AB93&lt;&gt;"S"),N(S93)," ")</f>
+      </c>
+      <c r="AI93" s="11" t="str">
+        <f>IF(AND(AD93&lt;&gt;"P",AB93="S"),N(S93)," ")</f>
+      </c>
+    </row>
+    <row r="94" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A94" s="101"/>
       <c r="B94" s="42"/>
       <c r="C94" s="75"/>
@@ -7629,8 +7903,14 @@
       <c r="AG94" s="11" t="str">
         <f>IF(AD94="P",N(S94)," ")</f>
       </c>
-    </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH94" s="11" t="str">
+        <f>IF(AND(AD94&lt;&gt;"P",AB94&lt;&gt;"S"),N(S94)," ")</f>
+      </c>
+      <c r="AI94" s="11" t="str">
+        <f>IF(AND(AD94&lt;&gt;"P",AB94="S"),N(S94)," ")</f>
+      </c>
+    </row>
+    <row r="95" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A95" s="101"/>
       <c r="B95" s="42"/>
       <c r="C95" s="75"/>
@@ -7704,8 +7984,14 @@
       <c r="AG95" s="11" t="str">
         <f>IF(AD95="P",N(S95)," ")</f>
       </c>
-    </row>
-    <row r="96" spans="1:33" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH95" s="11" t="str">
+        <f>IF(AND(AD95&lt;&gt;"P",AB95&lt;&gt;"S"),N(S95)," ")</f>
+      </c>
+      <c r="AI95" s="11" t="str">
+        <f>IF(AND(AD95&lt;&gt;"P",AB95="S"),N(S95)," ")</f>
+      </c>
+    </row>
+    <row r="96" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="101"/>
       <c r="B96" s="155" t="str">
         <f>B43</f>
@@ -7740,7 +8026,7 @@
       <c r="Z96" s="11"/>
       <c r="AA96" s="22"/>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A97" s="101"/>
       <c r="B97" s="42"/>
       <c r="C97" s="75"/>
@@ -7814,8 +8100,14 @@
       <c r="AG97" s="11" t="str">
         <f>IF(AD97="P",N(S97)," ")</f>
       </c>
-    </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH97" s="11" t="str">
+        <f>IF(AND(AD97&lt;&gt;"P",AB97&lt;&gt;"S"),N(S97)," ")</f>
+      </c>
+      <c r="AI97" s="11" t="str">
+        <f>IF(AND(AD97&lt;&gt;"P",AB97="S"),N(S97)," ")</f>
+      </c>
+    </row>
+    <row r="98" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A98" s="101"/>
       <c r="B98" s="42"/>
       <c r="C98" s="75"/>
@@ -7889,8 +8181,14 @@
       <c r="AG98" s="11" t="str">
         <f>IF(AD98="P",N(S98)," ")</f>
       </c>
-    </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH98" s="11" t="str">
+        <f>IF(AND(AD98&lt;&gt;"P",AB98&lt;&gt;"S"),N(S98)," ")</f>
+      </c>
+      <c r="AI98" s="11" t="str">
+        <f>IF(AND(AD98&lt;&gt;"P",AB98="S"),N(S98)," ")</f>
+      </c>
+    </row>
+    <row r="99" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A99" s="101"/>
       <c r="B99" s="42"/>
       <c r="C99" s="75"/>
@@ -7964,8 +8262,14 @@
       <c r="AG99" s="11" t="str">
         <f>IF(AD99="P",N(S99)," ")</f>
       </c>
-    </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH99" s="11" t="str">
+        <f>IF(AND(AD99&lt;&gt;"P",AB99&lt;&gt;"S"),N(S99)," ")</f>
+      </c>
+      <c r="AI99" s="11" t="str">
+        <f>IF(AND(AD99&lt;&gt;"P",AB99="S"),N(S99)," ")</f>
+      </c>
+    </row>
+    <row r="100" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A100" s="101"/>
       <c r="B100" s="42"/>
       <c r="C100" s="75"/>
@@ -8039,8 +8343,14 @@
       <c r="AG100" s="11" t="str">
         <f>IF(AD100="P",N(S100)," ")</f>
       </c>
-    </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH100" s="11" t="str">
+        <f>IF(AND(AD100&lt;&gt;"P",AB100&lt;&gt;"S"),N(S100)," ")</f>
+      </c>
+      <c r="AI100" s="11" t="str">
+        <f>IF(AND(AD100&lt;&gt;"P",AB100="S"),N(S100)," ")</f>
+      </c>
+    </row>
+    <row r="101" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A101" s="101"/>
       <c r="B101" s="42"/>
       <c r="C101" s="75"/>
@@ -8114,8 +8424,14 @@
       <c r="AG101" s="11" t="str">
         <f>IF(AD101="P",N(S101)," ")</f>
       </c>
-    </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.15">
+      <c r="AH101" s="11" t="str">
+        <f>IF(AND(AD101&lt;&gt;"P",AB101&lt;&gt;"S"),N(S101)," ")</f>
+      </c>
+      <c r="AI101" s="11" t="str">
+        <f>IF(AND(AD101&lt;&gt;"P",AB101="S"),N(S101)," ")</f>
+      </c>
+    </row>
+    <row r="102" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A102" s="101"/>
       <c r="B102" s="122" t="s">
         <v>54</v>
@@ -8146,7 +8462,7 @@
       <c r="Z102" s="11"/>
       <c r="AA102" s="22"/>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A103" s="101"/>
       <c r="B103" s="42"/>
       <c r="C103" s="75"/>
@@ -8210,7 +8526,7 @@
       </c>
       <c r="AA103" s="22"/>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A104" s="101"/>
       <c r="B104" s="42"/>
       <c r="C104" s="75"/>
@@ -8274,7 +8590,7 @@
       </c>
       <c r="AA104" s="22"/>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A105" s="101"/>
       <c r="B105" s="42"/>
       <c r="C105" s="75"/>
@@ -8338,7 +8654,7 @@
       </c>
       <c r="AA105" s="22"/>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A106" s="101"/>
       <c r="B106" s="42"/>
       <c r="C106" s="75"/>
@@ -8402,7 +8718,7 @@
       </c>
       <c r="AA106" s="22"/>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A107" s="101"/>
       <c r="B107" s="42"/>
       <c r="C107" s="75"/>
@@ -8466,7 +8782,7 @@
       </c>
       <c r="AA107" s="22"/>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A108" s="101"/>
       <c r="B108" s="117" t="s">
         <v>16</v>
@@ -8555,8 +8871,14 @@
       <c r="AG108" s="17">
         <f>SUM(AG91:AG107)</f>
       </c>
-    </row>
-    <row r="109" spans="1:33" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AH108" s="17">
+        <f>SUM(AH91:AH107)</f>
+      </c>
+      <c r="AI108" s="17">
+        <f>SUM(AI91:AI107)</f>
+      </c>
+    </row>
+    <row r="109" spans="1:35" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A109" s="101"/>
       <c r="B109" s="12"/>
       <c r="C109" s="77"/>
@@ -8585,7 +8907,7 @@
       <c r="Z109" s="11"/>
       <c r="AA109" s="22"/>
     </row>
-    <row r="110" spans="1:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:35" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A110" s="101"/>
       <c r="B110" s="152" t="str">
         <f>B59</f>
@@ -8678,8 +9000,14 @@
       <c r="AG110" s="19">
         <f>AG64+AG72+AG80+AG88+AG108</f>
       </c>
-    </row>
-    <row r="111" spans="1:33" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="AH110" s="19">
+        <f>AH64+AH72+AH80+AH88+AH108</f>
+      </c>
+      <c r="AI110" s="19">
+        <f>AI64+AI72+AI80+AI88+AI108</f>
+      </c>
+    </row>
+    <row r="111" spans="1:35" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A111" s="102"/>
       <c r="B111" s="24"/>
       <c r="C111" s="79"/>

--- a/packages/GB Accounts Self Employed 2023-04-05 (Apr23) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Self Employed 2023-04-05 (Apr23) Excel 2007/Fixedassets.xlsx
@@ -1781,7 +1781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AI111"/>
+  <dimension ref="A1:AI121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="5" customWidth="1"/>
@@ -9035,6 +9035,192 @@
       <c r="Y111" s="27"/>
       <c r="Z111" s="27"/>
       <c r="AA111" s="28"/>
+    </row>
+    <row r="113" spans="1:35" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B113" s="152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STRUCTURES AND BUILDINGS ALLOWANCE (SA103F boxes 53 and 53.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" spans="1:35" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date first in qualifying use</t>
+        </is>
+      </c>
+      <c r="C114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building name</t>
+        </is>
+      </c>
+      <c r="D114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="E114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qualifying expenditure</t>
+        </is>
+      </c>
+      <c r="F114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postcode</t>
+        </is>
+      </c>
+      <c r="G114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tax site (F = Freeport or Investment Zone)</t>
+        </is>
+      </c>
+      <c r="H114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate</t>
+        </is>
+      </c>
+      <c r="I114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date qualifying use ceased</t>
+        </is>
+      </c>
+      <c r="J114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Days claimed this year</t>
+        </is>
+      </c>
+      <c r="K114" s="130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allowance this year</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="B115" s="112"/>
+      <c r="C115" s="42"/>
+      <c r="D115" s="42"/>
+      <c r="E115" s="44"/>
+      <c r="F115" s="42"/>
+      <c r="G115" s="42"/>
+      <c r="H115" s="15" t="str">
+        <f>IF(E115&gt;0,IF(G115="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I115" s="112"/>
+      <c r="J115" s="11" t="str">
+        <f>IF(E115&gt;0,MAX(0,MIN($S$4,IF(N(I115)&gt;0,I115,$S$4),EDATE(B115,IF(G115="F",120,400))-1)-MAX($D$6,B115)+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="K115" s="11" t="str">
+        <f>IF(E115&gt;0,E115*H115*J115/($S$4-$D$6+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="116" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="B116" s="112"/>
+      <c r="C116" s="42"/>
+      <c r="D116" s="42"/>
+      <c r="E116" s="44"/>
+      <c r="F116" s="42"/>
+      <c r="G116" s="42"/>
+      <c r="H116" s="15" t="str">
+        <f>IF(E116&gt;0,IF(G116="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I116" s="112"/>
+      <c r="J116" s="11" t="str">
+        <f>IF(E116&gt;0,MAX(0,MIN($S$4,IF(N(I116)&gt;0,I116,$S$4),EDATE(B116,IF(G116="F",120,400))-1)-MAX($D$6,B116)+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="K116" s="11" t="str">
+        <f>IF(E116&gt;0,E116*H116*J116/($S$4-$D$6+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="117" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="B117" s="112"/>
+      <c r="C117" s="42"/>
+      <c r="D117" s="42"/>
+      <c r="E117" s="44"/>
+      <c r="F117" s="42"/>
+      <c r="G117" s="42"/>
+      <c r="H117" s="15" t="str">
+        <f>IF(E117&gt;0,IF(G117="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I117" s="112"/>
+      <c r="J117" s="11" t="str">
+        <f>IF(E117&gt;0,MAX(0,MIN($S$4,IF(N(I117)&gt;0,I117,$S$4),EDATE(B117,IF(G117="F",120,400))-1)-MAX($D$6,B117)+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="K117" s="11" t="str">
+        <f>IF(E117&gt;0,E117*H117*J117/($S$4-$D$6+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="118" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="B118" s="112"/>
+      <c r="C118" s="42"/>
+      <c r="D118" s="42"/>
+      <c r="E118" s="44"/>
+      <c r="F118" s="42"/>
+      <c r="G118" s="42"/>
+      <c r="H118" s="15" t="str">
+        <f>IF(E118&gt;0,IF(G118="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I118" s="112"/>
+      <c r="J118" s="11" t="str">
+        <f>IF(E118&gt;0,MAX(0,MIN($S$4,IF(N(I118)&gt;0,I118,$S$4),EDATE(B118,IF(G118="F",120,400))-1)-MAX($D$6,B118)+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="K118" s="11" t="str">
+        <f>IF(E118&gt;0,E118*H118*J118/($S$4-$D$6+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="119" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="B119" s="112"/>
+      <c r="C119" s="42"/>
+      <c r="D119" s="42"/>
+      <c r="E119" s="44"/>
+      <c r="F119" s="42"/>
+      <c r="G119" s="42"/>
+      <c r="H119" s="15" t="str">
+        <f>IF(E119&gt;0,IF(G119="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="I119" s="112"/>
+      <c r="J119" s="11" t="str">
+        <f>IF(E119&gt;0,MAX(0,MIN($S$4,IF(N(I119)&gt;0,I119,$S$4),EDATE(B119,IF(G119="F",120,400))-1)-MAX($D$6,B119)+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="K119" s="11" t="str">
+        <f>IF(E119&gt;0,E119*H119*J119/($S$4-$D$6+1)," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="120" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="B120" s="117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structures and Buildings Allowance (box 53)</t>
+        </is>
+      </c>
+      <c r="K120" s="17">
+        <f>SUMIF(G115:G119,"&lt;&gt;F",K115:K119)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="B121" s="117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freeport and Investment Zone SBA (box 53.1)</t>
+        </is>
+      </c>
+      <c r="K121" s="17">
+        <f>SUMIF(G115:G119,"F",K115:K119)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="56">
